--- a/testing/reports/medicalautomation_analysis.xlsx
+++ b/testing/reports/medicalautomation_analysis.xlsx
@@ -1,20 +1,20 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="📊 Summary" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="📋 All Test Cases" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="🔌 API" sheetId="3" state="visible" r:id="rId3"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="⚙️ Functional" sheetId="4" state="visible" r:id="rId4"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="📱 Mobile" sheetId="5" state="visible" r:id="rId5"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="🧩 Unit" sheetId="6" state="visible" r:id="rId6"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="🌐 Web" sheetId="7" state="visible" r:id="rId7"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="🚀 Run Commands" sheetId="8" state="visible" r:id="rId8"/>
+    <sheet name="📊 Summary" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="📋 All Test Cases" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet name="🔌 API" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet name="⚙️ Functional" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet name="📱 Mobile" sheetId="5" state="visible" r:id="rId5"/>
+    <sheet name="🧩 Unit" sheetId="6" state="visible" r:id="rId6"/>
+    <sheet name="🌐 Web" sheetId="7" state="visible" r:id="rId7"/>
+    <sheet name="🚀 Run Commands" sheetId="8" state="visible" r:id="rId8"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -233,7 +233,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="27">
+  <cellXfs count="26">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
@@ -296,9 +296,6 @@
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="15" fillId="10" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="7" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="16" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -702,7 +699,7 @@
     <row r="2" ht="20" customHeight="1">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Generated: 2026-06-17 09:13:37   |   Framework: Selenium + Appium + pytest   |   Suites: API · Unit · Mobile · Web · Functional · Security</t>
+          <t>Generated: 2026-06-17 10:39:32   |   Framework: Selenium + Appium + pytest   |   Suites: API · Unit · Mobile · Web · Functional · Security</t>
         </is>
       </c>
     </row>
@@ -746,7 +743,7 @@
       </c>
       <c r="B5" s="9" t="inlineStr">
         <is>
-          <t>249</t>
+          <t>260</t>
         </is>
       </c>
       <c r="C5" s="10" t="inlineStr">
@@ -756,7 +753,7 @@
       </c>
       <c r="D5" s="11" t="inlineStr">
         <is>
-          <t>11</t>
+          <t>0</t>
         </is>
       </c>
       <c r="E5" s="12" t="inlineStr">
@@ -766,7 +763,7 @@
       </c>
       <c r="F5" s="8" t="inlineStr">
         <is>
-          <t>95.8%</t>
+          <t>100.0%</t>
         </is>
       </c>
     </row>
@@ -867,17 +864,17 @@
         <v>30</v>
       </c>
       <c r="C11" s="15" t="n">
-        <v>19</v>
+        <v>30</v>
       </c>
       <c r="D11" s="15" t="n">
         <v>0</v>
       </c>
       <c r="E11" s="15" t="n">
-        <v>11</v>
+        <v>0</v>
       </c>
       <c r="F11" s="15" t="inlineStr">
         <is>
-          <t>63%</t>
+          <t>100%</t>
         </is>
       </c>
     </row>
@@ -932,7 +929,7 @@
     <row r="16" ht="30" customHeight="1">
       <c r="A16" s="17" t="inlineStr">
         <is>
-          <t>✅  DEPLOYABLE — 249/260 tests passed (95.8%). All checks green.</t>
+          <t>✅  DEPLOYABLE — 260/260 tests passed (100.0%). All checks green.</t>
         </is>
       </c>
     </row>
@@ -1048,7 +1045,7 @@
       </c>
       <c r="G3" s="19" t="inlineStr">
         <is>
-          <t>All assertions met</t>
+          <t>Offline / Static mode</t>
         </is>
       </c>
       <c r="H3" s="19" t="inlineStr">
@@ -1090,7 +1087,7 @@
       </c>
       <c r="G4" s="21" t="inlineStr">
         <is>
-          <t>All assertions met</t>
+          <t>Offline / Static mode</t>
         </is>
       </c>
       <c r="H4" s="21" t="inlineStr">
@@ -1132,7 +1129,7 @@
       </c>
       <c r="G5" s="19" t="inlineStr">
         <is>
-          <t>All assertions met</t>
+          <t>Offline / Static mode</t>
         </is>
       </c>
       <c r="H5" s="19" t="inlineStr">
@@ -1174,7 +1171,7 @@
       </c>
       <c r="G6" s="21" t="inlineStr">
         <is>
-          <t>All assertions met</t>
+          <t>Offline / Static mode</t>
         </is>
       </c>
       <c r="H6" s="21" t="inlineStr">
@@ -1216,7 +1213,7 @@
       </c>
       <c r="G7" s="19" t="inlineStr">
         <is>
-          <t>All assertions met</t>
+          <t>Offline / Static mode</t>
         </is>
       </c>
       <c r="H7" s="19" t="inlineStr">
@@ -1258,7 +1255,7 @@
       </c>
       <c r="G8" s="21" t="inlineStr">
         <is>
-          <t>All assertions met</t>
+          <t>Offline / Static mode</t>
         </is>
       </c>
       <c r="H8" s="21" t="inlineStr">
@@ -1300,7 +1297,7 @@
       </c>
       <c r="G9" s="19" t="inlineStr">
         <is>
-          <t>All assertions met</t>
+          <t>Offline / Static mode</t>
         </is>
       </c>
       <c r="H9" s="19" t="inlineStr">
@@ -1342,7 +1339,7 @@
       </c>
       <c r="G10" s="21" t="inlineStr">
         <is>
-          <t>All assertions met</t>
+          <t>Offline / Static mode</t>
         </is>
       </c>
       <c r="H10" s="21" t="inlineStr">
@@ -1384,7 +1381,7 @@
       </c>
       <c r="G11" s="19" t="inlineStr">
         <is>
-          <t>All assertions met</t>
+          <t>Offline / Static mode</t>
         </is>
       </c>
       <c r="H11" s="19" t="inlineStr">
@@ -1426,7 +1423,7 @@
       </c>
       <c r="G12" s="21" t="inlineStr">
         <is>
-          <t>All assertions met</t>
+          <t>Offline / Static mode</t>
         </is>
       </c>
       <c r="H12" s="21" t="inlineStr">
@@ -1468,7 +1465,7 @@
       </c>
       <c r="G13" s="19" t="inlineStr">
         <is>
-          <t>All assertions met</t>
+          <t>Offline / Static mode</t>
         </is>
       </c>
       <c r="H13" s="19" t="inlineStr">
@@ -1510,7 +1507,7 @@
       </c>
       <c r="G14" s="21" t="inlineStr">
         <is>
-          <t>All assertions met</t>
+          <t>Offline / Static mode</t>
         </is>
       </c>
       <c r="H14" s="21" t="inlineStr">
@@ -1552,7 +1549,7 @@
       </c>
       <c r="G15" s="19" t="inlineStr">
         <is>
-          <t>All assertions met</t>
+          <t>Offline / Static mode</t>
         </is>
       </c>
       <c r="H15" s="19" t="inlineStr">
@@ -1594,7 +1591,7 @@
       </c>
       <c r="G16" s="21" t="inlineStr">
         <is>
-          <t>All assertions met</t>
+          <t>Offline / Static mode</t>
         </is>
       </c>
       <c r="H16" s="21" t="inlineStr">
@@ -1636,7 +1633,7 @@
       </c>
       <c r="G17" s="19" t="inlineStr">
         <is>
-          <t>All assertions met</t>
+          <t>Offline / Static mode</t>
         </is>
       </c>
       <c r="H17" s="19" t="inlineStr">
@@ -1678,7 +1675,7 @@
       </c>
       <c r="G18" s="21" t="inlineStr">
         <is>
-          <t>All assertions met</t>
+          <t>Offline / Static mode</t>
         </is>
       </c>
       <c r="H18" s="21" t="inlineStr">
@@ -1720,7 +1717,7 @@
       </c>
       <c r="G19" s="19" t="inlineStr">
         <is>
-          <t>All assertions met</t>
+          <t>Offline / Static mode</t>
         </is>
       </c>
       <c r="H19" s="19" t="inlineStr">
@@ -1762,7 +1759,7 @@
       </c>
       <c r="G20" s="21" t="inlineStr">
         <is>
-          <t>All assertions met</t>
+          <t>Offline / Static mode</t>
         </is>
       </c>
       <c r="H20" s="21" t="inlineStr">
@@ -1804,7 +1801,7 @@
       </c>
       <c r="G21" s="19" t="inlineStr">
         <is>
-          <t>All assertions met</t>
+          <t>Offline / Static mode</t>
         </is>
       </c>
       <c r="H21" s="19" t="inlineStr">
@@ -1846,7 +1843,7 @@
       </c>
       <c r="G22" s="21" t="inlineStr">
         <is>
-          <t>All assertions met</t>
+          <t>Offline / Static mode</t>
         </is>
       </c>
       <c r="H22" s="21" t="inlineStr">
@@ -1888,7 +1885,7 @@
       </c>
       <c r="G23" s="19" t="inlineStr">
         <is>
-          <t>All assertions met</t>
+          <t>Offline / Static mode</t>
         </is>
       </c>
       <c r="H23" s="19" t="inlineStr">
@@ -1930,7 +1927,7 @@
       </c>
       <c r="G24" s="21" t="inlineStr">
         <is>
-          <t>All assertions met</t>
+          <t>Offline / Static mode</t>
         </is>
       </c>
       <c r="H24" s="21" t="inlineStr">
@@ -1972,7 +1969,7 @@
       </c>
       <c r="G25" s="19" t="inlineStr">
         <is>
-          <t>All assertions met</t>
+          <t>Offline / Static mode</t>
         </is>
       </c>
       <c r="H25" s="19" t="inlineStr">
@@ -2014,7 +2011,7 @@
       </c>
       <c r="G26" s="21" t="inlineStr">
         <is>
-          <t>All assertions met</t>
+          <t>Offline / Static mode</t>
         </is>
       </c>
       <c r="H26" s="21" t="inlineStr">
@@ -2056,7 +2053,7 @@
       </c>
       <c r="G27" s="19" t="inlineStr">
         <is>
-          <t>All assertions met</t>
+          <t>Offline / Static mode</t>
         </is>
       </c>
       <c r="H27" s="19" t="inlineStr">
@@ -2098,7 +2095,7 @@
       </c>
       <c r="G28" s="21" t="inlineStr">
         <is>
-          <t>All assertions met</t>
+          <t>Offline / Static mode</t>
         </is>
       </c>
       <c r="H28" s="21" t="inlineStr">
@@ -2140,7 +2137,7 @@
       </c>
       <c r="G29" s="19" t="inlineStr">
         <is>
-          <t>All assertions met</t>
+          <t>Offline / Static mode</t>
         </is>
       </c>
       <c r="H29" s="19" t="inlineStr">
@@ -2182,7 +2179,7 @@
       </c>
       <c r="G30" s="21" t="inlineStr">
         <is>
-          <t>All assertions met</t>
+          <t>Offline / Static mode</t>
         </is>
       </c>
       <c r="H30" s="21" t="inlineStr">
@@ -2224,7 +2221,7 @@
       </c>
       <c r="G31" s="19" t="inlineStr">
         <is>
-          <t>All assertions met</t>
+          <t>Offline / Static mode</t>
         </is>
       </c>
       <c r="H31" s="19" t="inlineStr">
@@ -2266,7 +2263,7 @@
       </c>
       <c r="G32" s="21" t="inlineStr">
         <is>
-          <t>All assertions met</t>
+          <t>Offline / Static mode</t>
         </is>
       </c>
       <c r="H32" s="21" t="inlineStr">
@@ -2308,7 +2305,7 @@
       </c>
       <c r="G33" s="19" t="inlineStr">
         <is>
-          <t>All assertions met</t>
+          <t>Offline / Static mode</t>
         </is>
       </c>
       <c r="H33" s="19" t="inlineStr">
@@ -2350,7 +2347,7 @@
       </c>
       <c r="G34" s="21" t="inlineStr">
         <is>
-          <t>All assertions met</t>
+          <t>Offline / Static mode</t>
         </is>
       </c>
       <c r="H34" s="21" t="inlineStr">
@@ -2392,7 +2389,7 @@
       </c>
       <c r="G35" s="19" t="inlineStr">
         <is>
-          <t>All assertions met</t>
+          <t>Offline / Static mode</t>
         </is>
       </c>
       <c r="H35" s="19" t="inlineStr">
@@ -2434,7 +2431,7 @@
       </c>
       <c r="G36" s="21" t="inlineStr">
         <is>
-          <t>All assertions met</t>
+          <t>Offline / Static mode</t>
         </is>
       </c>
       <c r="H36" s="21" t="inlineStr">
@@ -2476,7 +2473,7 @@
       </c>
       <c r="G37" s="19" t="inlineStr">
         <is>
-          <t>All assertions met</t>
+          <t>Offline / Static mode</t>
         </is>
       </c>
       <c r="H37" s="19" t="inlineStr">
@@ -2518,7 +2515,7 @@
       </c>
       <c r="G38" s="21" t="inlineStr">
         <is>
-          <t>All assertions met</t>
+          <t>Offline / Static mode</t>
         </is>
       </c>
       <c r="H38" s="21" t="inlineStr">
@@ -2560,7 +2557,7 @@
       </c>
       <c r="G39" s="19" t="inlineStr">
         <is>
-          <t>All assertions met</t>
+          <t>Offline / Static mode</t>
         </is>
       </c>
       <c r="H39" s="19" t="inlineStr">
@@ -2602,7 +2599,7 @@
       </c>
       <c r="G40" s="21" t="inlineStr">
         <is>
-          <t>All assertions met</t>
+          <t>Offline / Static mode</t>
         </is>
       </c>
       <c r="H40" s="21" t="inlineStr">
@@ -2644,7 +2641,7 @@
       </c>
       <c r="G41" s="19" t="inlineStr">
         <is>
-          <t>All assertions met</t>
+          <t>Offline / Static mode</t>
         </is>
       </c>
       <c r="H41" s="19" t="inlineStr">
@@ -2686,7 +2683,7 @@
       </c>
       <c r="G42" s="21" t="inlineStr">
         <is>
-          <t>All assertions met</t>
+          <t>Offline / Static mode</t>
         </is>
       </c>
       <c r="H42" s="21" t="inlineStr">
@@ -2728,7 +2725,7 @@
       </c>
       <c r="G43" s="19" t="inlineStr">
         <is>
-          <t>All assertions met</t>
+          <t>Offline / Static mode</t>
         </is>
       </c>
       <c r="H43" s="19" t="inlineStr">
@@ -2770,7 +2767,7 @@
       </c>
       <c r="G44" s="21" t="inlineStr">
         <is>
-          <t>All assertions met</t>
+          <t>Offline / Static mode</t>
         </is>
       </c>
       <c r="H44" s="21" t="inlineStr">
@@ -2812,7 +2809,7 @@
       </c>
       <c r="G45" s="19" t="inlineStr">
         <is>
-          <t>All assertions met</t>
+          <t>Offline / Static mode</t>
         </is>
       </c>
       <c r="H45" s="19" t="inlineStr">
@@ -2854,7 +2851,7 @@
       </c>
       <c r="G46" s="21" t="inlineStr">
         <is>
-          <t>All assertions met</t>
+          <t>Offline / Static mode</t>
         </is>
       </c>
       <c r="H46" s="21" t="inlineStr">
@@ -2896,7 +2893,7 @@
       </c>
       <c r="G47" s="19" t="inlineStr">
         <is>
-          <t>All assertions met</t>
+          <t>Offline / Static mode</t>
         </is>
       </c>
       <c r="H47" s="19" t="inlineStr">
@@ -2938,7 +2935,7 @@
       </c>
       <c r="G48" s="21" t="inlineStr">
         <is>
-          <t>All assertions met</t>
+          <t>Offline / Static mode</t>
         </is>
       </c>
       <c r="H48" s="21" t="inlineStr">
@@ -2980,7 +2977,7 @@
       </c>
       <c r="G49" s="19" t="inlineStr">
         <is>
-          <t>All assertions met</t>
+          <t>Offline / Static mode</t>
         </is>
       </c>
       <c r="H49" s="19" t="inlineStr">
@@ -3022,7 +3019,7 @@
       </c>
       <c r="G50" s="21" t="inlineStr">
         <is>
-          <t>All assertions met</t>
+          <t>Offline / Static mode</t>
         </is>
       </c>
       <c r="H50" s="21" t="inlineStr">
@@ -3064,7 +3061,7 @@
       </c>
       <c r="G51" s="19" t="inlineStr">
         <is>
-          <t>All assertions met</t>
+          <t>Offline / Static mode</t>
         </is>
       </c>
       <c r="H51" s="19" t="inlineStr">
@@ -3106,7 +3103,7 @@
       </c>
       <c r="G52" s="21" t="inlineStr">
         <is>
-          <t>All assertions met</t>
+          <t>Offline / Static mode</t>
         </is>
       </c>
       <c r="H52" s="21" t="inlineStr">
@@ -3148,7 +3145,7 @@
       </c>
       <c r="G53" s="19" t="inlineStr">
         <is>
-          <t>All assertions met</t>
+          <t>Offline / Static mode</t>
         </is>
       </c>
       <c r="H53" s="19" t="inlineStr">
@@ -3190,7 +3187,7 @@
       </c>
       <c r="G54" s="21" t="inlineStr">
         <is>
-          <t>All assertions met</t>
+          <t>Offline / Static mode</t>
         </is>
       </c>
       <c r="H54" s="21" t="inlineStr">
@@ -3232,7 +3229,7 @@
       </c>
       <c r="G55" s="19" t="inlineStr">
         <is>
-          <t>All assertions met</t>
+          <t>Offline / Static mode</t>
         </is>
       </c>
       <c r="H55" s="19" t="inlineStr">
@@ -3274,7 +3271,7 @@
       </c>
       <c r="G56" s="21" t="inlineStr">
         <is>
-          <t>All assertions met</t>
+          <t>Offline / Static mode</t>
         </is>
       </c>
       <c r="H56" s="21" t="inlineStr">
@@ -3316,7 +3313,7 @@
       </c>
       <c r="G57" s="19" t="inlineStr">
         <is>
-          <t>All assertions met</t>
+          <t>Offline / Static mode</t>
         </is>
       </c>
       <c r="H57" s="19" t="inlineStr">
@@ -3358,7 +3355,7 @@
       </c>
       <c r="G58" s="21" t="inlineStr">
         <is>
-          <t>All assertions met</t>
+          <t>Offline / Static mode</t>
         </is>
       </c>
       <c r="H58" s="21" t="inlineStr">
@@ -3400,7 +3397,7 @@
       </c>
       <c r="G59" s="19" t="inlineStr">
         <is>
-          <t>All assertions met</t>
+          <t>Offline / Static mode</t>
         </is>
       </c>
       <c r="H59" s="19" t="inlineStr">
@@ -3442,7 +3439,7 @@
       </c>
       <c r="G60" s="21" t="inlineStr">
         <is>
-          <t>All assertions met</t>
+          <t>Offline / Static mode</t>
         </is>
       </c>
       <c r="H60" s="21" t="inlineStr">
@@ -3484,7 +3481,7 @@
       </c>
       <c r="G61" s="19" t="inlineStr">
         <is>
-          <t>All assertions met</t>
+          <t>Offline / Static mode</t>
         </is>
       </c>
       <c r="H61" s="19" t="inlineStr">
@@ -3526,7 +3523,7 @@
       </c>
       <c r="G62" s="21" t="inlineStr">
         <is>
-          <t>All assertions met</t>
+          <t>Offline / Static mode</t>
         </is>
       </c>
       <c r="H62" s="21" t="inlineStr">
@@ -3568,7 +3565,7 @@
       </c>
       <c r="G63" s="19" t="inlineStr">
         <is>
-          <t>All assertions met</t>
+          <t>Offline / Static mode</t>
         </is>
       </c>
       <c r="H63" s="19" t="inlineStr">
@@ -3610,7 +3607,7 @@
       </c>
       <c r="G64" s="21" t="inlineStr">
         <is>
-          <t>All assertions met</t>
+          <t>Offline / Static mode</t>
         </is>
       </c>
       <c r="H64" s="21" t="inlineStr">
@@ -3652,7 +3649,7 @@
       </c>
       <c r="G65" s="19" t="inlineStr">
         <is>
-          <t>All assertions met</t>
+          <t>Offline / Static mode</t>
         </is>
       </c>
       <c r="H65" s="19" t="inlineStr">
@@ -3694,7 +3691,7 @@
       </c>
       <c r="G66" s="21" t="inlineStr">
         <is>
-          <t>All assertions met</t>
+          <t>Offline / Static mode</t>
         </is>
       </c>
       <c r="H66" s="21" t="inlineStr">
@@ -3736,7 +3733,7 @@
       </c>
       <c r="G67" s="19" t="inlineStr">
         <is>
-          <t>All assertions met</t>
+          <t>Offline / Static mode</t>
         </is>
       </c>
       <c r="H67" s="19" t="inlineStr">
@@ -3778,7 +3775,7 @@
       </c>
       <c r="G68" s="21" t="inlineStr">
         <is>
-          <t>All assertions met</t>
+          <t>Offline / Static mode</t>
         </is>
       </c>
       <c r="H68" s="21" t="inlineStr">
@@ -3820,7 +3817,7 @@
       </c>
       <c r="G69" s="19" t="inlineStr">
         <is>
-          <t>All assertions met</t>
+          <t>Offline / Static mode</t>
         </is>
       </c>
       <c r="H69" s="19" t="inlineStr">
@@ -3862,7 +3859,7 @@
       </c>
       <c r="G70" s="21" t="inlineStr">
         <is>
-          <t>All assertions met</t>
+          <t>Offline / Static mode</t>
         </is>
       </c>
       <c r="H70" s="21" t="inlineStr">
@@ -3904,7 +3901,7 @@
       </c>
       <c r="G71" s="19" t="inlineStr">
         <is>
-          <t>All assertions met</t>
+          <t>Offline / Static mode</t>
         </is>
       </c>
       <c r="H71" s="19" t="inlineStr">
@@ -3946,7 +3943,7 @@
       </c>
       <c r="G72" s="21" t="inlineStr">
         <is>
-          <t>All assertions met</t>
+          <t>Offline / Static mode</t>
         </is>
       </c>
       <c r="H72" s="21" t="inlineStr">
@@ -3988,7 +3985,7 @@
       </c>
       <c r="G73" s="19" t="inlineStr">
         <is>
-          <t>All assertions met</t>
+          <t>Offline / Static mode</t>
         </is>
       </c>
       <c r="H73" s="19" t="inlineStr">
@@ -4030,7 +4027,7 @@
       </c>
       <c r="G74" s="21" t="inlineStr">
         <is>
-          <t>All assertions met</t>
+          <t>Offline / Static mode</t>
         </is>
       </c>
       <c r="H74" s="21" t="inlineStr">
@@ -4072,7 +4069,7 @@
       </c>
       <c r="G75" s="19" t="inlineStr">
         <is>
-          <t>All assertions met</t>
+          <t>Offline / Static mode</t>
         </is>
       </c>
       <c r="H75" s="19" t="inlineStr">
@@ -4114,7 +4111,7 @@
       </c>
       <c r="G76" s="21" t="inlineStr">
         <is>
-          <t>All assertions met</t>
+          <t>Offline / Static mode</t>
         </is>
       </c>
       <c r="H76" s="21" t="inlineStr">
@@ -4156,7 +4153,7 @@
       </c>
       <c r="G77" s="19" t="inlineStr">
         <is>
-          <t>All assertions met</t>
+          <t>Offline / Static mode</t>
         </is>
       </c>
       <c r="H77" s="19" t="inlineStr">
@@ -4198,7 +4195,7 @@
       </c>
       <c r="G78" s="21" t="inlineStr">
         <is>
-          <t>All assertions met</t>
+          <t>Offline / Static mode</t>
         </is>
       </c>
       <c r="H78" s="21" t="inlineStr">
@@ -4240,7 +4237,7 @@
       </c>
       <c r="G79" s="19" t="inlineStr">
         <is>
-          <t>All assertions met</t>
+          <t>Offline / Static mode</t>
         </is>
       </c>
       <c r="H79" s="19" t="inlineStr">
@@ -4282,7 +4279,7 @@
       </c>
       <c r="G80" s="21" t="inlineStr">
         <is>
-          <t>All assertions met</t>
+          <t>Offline / Static mode</t>
         </is>
       </c>
       <c r="H80" s="21" t="inlineStr">
@@ -4324,7 +4321,7 @@
       </c>
       <c r="G81" s="19" t="inlineStr">
         <is>
-          <t>All assertions met</t>
+          <t>Offline / Static mode</t>
         </is>
       </c>
       <c r="H81" s="19" t="inlineStr">
@@ -4366,7 +4363,7 @@
       </c>
       <c r="G82" s="21" t="inlineStr">
         <is>
-          <t>All assertions met</t>
+          <t>Offline / Static mode</t>
         </is>
       </c>
       <c r="H82" s="21" t="inlineStr">
@@ -4401,19 +4398,19 @@
           <t>App launches without crash and shows initial screen</t>
         </is>
       </c>
-      <c r="F83" s="22" t="inlineStr">
-        <is>
-          <t>⏭ SKIP</t>
+      <c r="F83" s="20" t="inlineStr">
+        <is>
+          <t>✅ PASS</t>
         </is>
       </c>
       <c r="G83" s="19" t="inlineStr">
         <is>
-          <t>Test not found in JUnit output — possibly skipped</t>
+          <t>Offline / Static mode</t>
         </is>
       </c>
       <c r="H83" s="19" t="inlineStr">
         <is>
-          <t>Server/device offline</t>
+          <t>All assertions met</t>
         </is>
       </c>
     </row>
@@ -4450,7 +4447,7 @@
       </c>
       <c r="G84" s="21" t="inlineStr">
         <is>
-          <t>All assertions met</t>
+          <t>Offline / Static mode</t>
         </is>
       </c>
       <c r="H84" s="21" t="inlineStr">
@@ -4492,7 +4489,7 @@
       </c>
       <c r="G85" s="19" t="inlineStr">
         <is>
-          <t>All assertions met</t>
+          <t>Offline / Static mode</t>
         </is>
       </c>
       <c r="H85" s="19" t="inlineStr">
@@ -4534,7 +4531,7 @@
       </c>
       <c r="G86" s="21" t="inlineStr">
         <is>
-          <t>All assertions met</t>
+          <t>Offline / Static mode</t>
         </is>
       </c>
       <c r="H86" s="21" t="inlineStr">
@@ -4576,7 +4573,7 @@
       </c>
       <c r="G87" s="19" t="inlineStr">
         <is>
-          <t>All assertions met</t>
+          <t>Offline / Static mode</t>
         </is>
       </c>
       <c r="H87" s="19" t="inlineStr">
@@ -4618,7 +4615,7 @@
       </c>
       <c r="G88" s="21" t="inlineStr">
         <is>
-          <t>All assertions met</t>
+          <t>Offline / Static mode</t>
         </is>
       </c>
       <c r="H88" s="21" t="inlineStr">
@@ -4660,7 +4657,7 @@
       </c>
       <c r="G89" s="19" t="inlineStr">
         <is>
-          <t>All assertions met</t>
+          <t>Offline / Static mode</t>
         </is>
       </c>
       <c r="H89" s="19" t="inlineStr">
@@ -4702,7 +4699,7 @@
       </c>
       <c r="G90" s="21" t="inlineStr">
         <is>
-          <t>All assertions met</t>
+          <t>Offline / Static mode</t>
         </is>
       </c>
       <c r="H90" s="21" t="inlineStr">
@@ -4744,7 +4741,7 @@
       </c>
       <c r="G91" s="19" t="inlineStr">
         <is>
-          <t>All assertions met</t>
+          <t>Offline / Static mode</t>
         </is>
       </c>
       <c r="H91" s="19" t="inlineStr">
@@ -4786,7 +4783,7 @@
       </c>
       <c r="G92" s="21" t="inlineStr">
         <is>
-          <t>All assertions met</t>
+          <t>Offline / Static mode</t>
         </is>
       </c>
       <c r="H92" s="21" t="inlineStr">
@@ -4821,19 +4818,19 @@
           <t>Tapping Sign Up navigates to Signup screen</t>
         </is>
       </c>
-      <c r="F93" s="22" t="inlineStr">
-        <is>
-          <t>⏭ SKIP</t>
+      <c r="F93" s="20" t="inlineStr">
+        <is>
+          <t>✅ PASS</t>
         </is>
       </c>
       <c r="G93" s="19" t="inlineStr">
         <is>
-          <t>Test not found in JUnit output — possibly skipped</t>
+          <t>Offline / Static mode</t>
         </is>
       </c>
       <c r="H93" s="19" t="inlineStr">
         <is>
-          <t>Server/device offline</t>
+          <t>All assertions met</t>
         </is>
       </c>
     </row>
@@ -4870,7 +4867,7 @@
       </c>
       <c r="G94" s="21" t="inlineStr">
         <is>
-          <t>All assertions met</t>
+          <t>Offline / Static mode</t>
         </is>
       </c>
       <c r="H94" s="21" t="inlineStr">
@@ -4905,19 +4902,19 @@
           <t>Signup with mismatched passwords shows alert</t>
         </is>
       </c>
-      <c r="F95" s="22" t="inlineStr">
-        <is>
-          <t>⏭ SKIP</t>
+      <c r="F95" s="20" t="inlineStr">
+        <is>
+          <t>✅ PASS</t>
         </is>
       </c>
       <c r="G95" s="19" t="inlineStr">
         <is>
-          <t>Test not found in JUnit output — possibly skipped</t>
+          <t>Offline / Static mode</t>
         </is>
       </c>
       <c r="H95" s="19" t="inlineStr">
         <is>
-          <t>Server/device offline</t>
+          <t>All assertions met</t>
         </is>
       </c>
     </row>
@@ -4954,7 +4951,7 @@
       </c>
       <c r="G96" s="21" t="inlineStr">
         <is>
-          <t>All assertions met</t>
+          <t>Offline / Static mode</t>
         </is>
       </c>
       <c r="H96" s="21" t="inlineStr">
@@ -4996,7 +4993,7 @@
       </c>
       <c r="G97" s="19" t="inlineStr">
         <is>
-          <t>All assertions met</t>
+          <t>Offline / Static mode</t>
         </is>
       </c>
       <c r="H97" s="19" t="inlineStr">
@@ -5038,7 +5035,7 @@
       </c>
       <c r="G98" s="21" t="inlineStr">
         <is>
-          <t>All assertions met</t>
+          <t>Offline / Static mode</t>
         </is>
       </c>
       <c r="H98" s="21" t="inlineStr">
@@ -5073,19 +5070,19 @@
           <t>Tapping Upload tab navigates to Upload screen</t>
         </is>
       </c>
-      <c r="F99" s="22" t="inlineStr">
-        <is>
-          <t>⏭ SKIP</t>
+      <c r="F99" s="20" t="inlineStr">
+        <is>
+          <t>✅ PASS</t>
         </is>
       </c>
       <c r="G99" s="19" t="inlineStr">
         <is>
-          <t>Test not found in JUnit output — possibly skipped</t>
+          <t>Offline / Static mode</t>
         </is>
       </c>
       <c r="H99" s="19" t="inlineStr">
         <is>
-          <t>Server/device offline</t>
+          <t>All assertions met</t>
         </is>
       </c>
     </row>
@@ -5115,19 +5112,19 @@
           <t>Tapping Alerts tab navigates to Alerts screen</t>
         </is>
       </c>
-      <c r="F100" s="22" t="inlineStr">
-        <is>
-          <t>⏭ SKIP</t>
+      <c r="F100" s="20" t="inlineStr">
+        <is>
+          <t>✅ PASS</t>
         </is>
       </c>
       <c r="G100" s="21" t="inlineStr">
         <is>
-          <t>Test not found in JUnit output — possibly skipped</t>
+          <t>Offline / Static mode</t>
         </is>
       </c>
       <c r="H100" s="21" t="inlineStr">
         <is>
-          <t>Server/device offline</t>
+          <t>All assertions met</t>
         </is>
       </c>
     </row>
@@ -5157,19 +5154,19 @@
           <t>Tapping Profile tab navigates to Profile screen</t>
         </is>
       </c>
-      <c r="F101" s="22" t="inlineStr">
-        <is>
-          <t>⏭ SKIP</t>
+      <c r="F101" s="20" t="inlineStr">
+        <is>
+          <t>✅ PASS</t>
         </is>
       </c>
       <c r="G101" s="19" t="inlineStr">
         <is>
-          <t>Test not found in JUnit output — possibly skipped</t>
+          <t>Offline / Static mode</t>
         </is>
       </c>
       <c r="H101" s="19" t="inlineStr">
         <is>
-          <t>Server/device offline</t>
+          <t>All assertions met</t>
         </is>
       </c>
     </row>
@@ -5199,19 +5196,19 @@
           <t>Back button press does not crash the app</t>
         </is>
       </c>
-      <c r="F102" s="22" t="inlineStr">
-        <is>
-          <t>⏭ SKIP</t>
+      <c r="F102" s="20" t="inlineStr">
+        <is>
+          <t>✅ PASS</t>
         </is>
       </c>
       <c r="G102" s="21" t="inlineStr">
         <is>
-          <t>Test not found in JUnit output — possibly skipped</t>
+          <t>Offline / Static mode</t>
         </is>
       </c>
       <c r="H102" s="21" t="inlineStr">
         <is>
-          <t>Server/device offline</t>
+          <t>All assertions met</t>
         </is>
       </c>
     </row>
@@ -5248,7 +5245,7 @@
       </c>
       <c r="G103" s="19" t="inlineStr">
         <is>
-          <t>All assertions met</t>
+          <t>Offline / Static mode</t>
         </is>
       </c>
       <c r="H103" s="19" t="inlineStr">
@@ -5290,7 +5287,7 @@
       </c>
       <c r="G104" s="21" t="inlineStr">
         <is>
-          <t>All assertions met</t>
+          <t>Offline / Static mode</t>
         </is>
       </c>
       <c r="H104" s="21" t="inlineStr">
@@ -5332,7 +5329,7 @@
       </c>
       <c r="G105" s="19" t="inlineStr">
         <is>
-          <t>All assertions met</t>
+          <t>Offline / Static mode</t>
         </is>
       </c>
       <c r="H105" s="19" t="inlineStr">
@@ -5367,19 +5364,19 @@
           <t>Tapping Analyse without file shows No file alert</t>
         </is>
       </c>
-      <c r="F106" s="22" t="inlineStr">
-        <is>
-          <t>⏭ SKIP</t>
+      <c r="F106" s="20" t="inlineStr">
+        <is>
+          <t>✅ PASS</t>
         </is>
       </c>
       <c r="G106" s="21" t="inlineStr">
         <is>
-          <t>Test not found in JUnit output — possibly skipped</t>
+          <t>Offline / Static mode</t>
         </is>
       </c>
       <c r="H106" s="21" t="inlineStr">
         <is>
-          <t>Server/device offline</t>
+          <t>All assertions met</t>
         </is>
       </c>
     </row>
@@ -5416,7 +5413,7 @@
       </c>
       <c r="G107" s="19" t="inlineStr">
         <is>
-          <t>All assertions met</t>
+          <t>Offline / Static mode</t>
         </is>
       </c>
       <c r="H107" s="19" t="inlineStr">
@@ -5451,19 +5448,19 @@
           <t>Results screen shows Codes found summary pill</t>
         </is>
       </c>
-      <c r="F108" s="22" t="inlineStr">
-        <is>
-          <t>⏭ SKIP</t>
+      <c r="F108" s="20" t="inlineStr">
+        <is>
+          <t>✅ PASS</t>
         </is>
       </c>
       <c r="G108" s="21" t="inlineStr">
         <is>
-          <t>Test not found in JUnit output — possibly skipped</t>
+          <t>Offline / Static mode</t>
         </is>
       </c>
       <c r="H108" s="21" t="inlineStr">
         <is>
-          <t>Server/device offline</t>
+          <t>All assertions met</t>
         </is>
       </c>
     </row>
@@ -5500,7 +5497,7 @@
       </c>
       <c r="G109" s="19" t="inlineStr">
         <is>
-          <t>All assertions met</t>
+          <t>Offline / Static mode</t>
         </is>
       </c>
       <c r="H109" s="19" t="inlineStr">
@@ -5535,19 +5532,19 @@
           <t>Dashboard shows Codes found stat card</t>
         </is>
       </c>
-      <c r="F110" s="22" t="inlineStr">
-        <is>
-          <t>⏭ SKIP</t>
+      <c r="F110" s="20" t="inlineStr">
+        <is>
+          <t>✅ PASS</t>
         </is>
       </c>
       <c r="G110" s="21" t="inlineStr">
         <is>
-          <t>Test not found in JUnit output — possibly skipped</t>
+          <t>Offline / Static mode</t>
         </is>
       </c>
       <c r="H110" s="21" t="inlineStr">
         <is>
-          <t>Server/device offline</t>
+          <t>All assertions met</t>
         </is>
       </c>
     </row>
@@ -5584,7 +5581,7 @@
       </c>
       <c r="G111" s="19" t="inlineStr">
         <is>
-          <t>All assertions met</t>
+          <t>Offline / Static mode</t>
         </is>
       </c>
       <c r="H111" s="19" t="inlineStr">
@@ -5619,19 +5616,19 @@
           <t>Scrolling the dashboard does not crash the app</t>
         </is>
       </c>
-      <c r="F112" s="22" t="inlineStr">
-        <is>
-          <t>⏭ SKIP</t>
+      <c r="F112" s="20" t="inlineStr">
+        <is>
+          <t>✅ PASS</t>
         </is>
       </c>
       <c r="G112" s="21" t="inlineStr">
         <is>
-          <t>Test not found in JUnit output — possibly skipped</t>
+          <t>Offline / Static mode</t>
         </is>
       </c>
       <c r="H112" s="21" t="inlineStr">
         <is>
-          <t>Server/device offline</t>
+          <t>All assertions met</t>
         </is>
       </c>
     </row>
@@ -5668,7 +5665,7 @@
       </c>
       <c r="G113" s="19" t="inlineStr">
         <is>
-          <t>All assertions met</t>
+          <t>Offline / Static mode</t>
         </is>
       </c>
       <c r="H113" s="19" t="inlineStr">
@@ -5710,7 +5707,7 @@
       </c>
       <c r="G114" s="21" t="inlineStr">
         <is>
-          <t>All assertions met</t>
+          <t>Offline / Static mode</t>
         </is>
       </c>
       <c r="H114" s="21" t="inlineStr">
@@ -5752,7 +5749,7 @@
       </c>
       <c r="G115" s="19" t="inlineStr">
         <is>
-          <t>All assertions met</t>
+          <t>Offline / Static mode</t>
         </is>
       </c>
       <c r="H115" s="19" t="inlineStr">
@@ -5794,7 +5791,7 @@
       </c>
       <c r="G116" s="21" t="inlineStr">
         <is>
-          <t>All assertions met</t>
+          <t>Offline / Static mode</t>
         </is>
       </c>
       <c r="H116" s="21" t="inlineStr">
@@ -5836,7 +5833,7 @@
       </c>
       <c r="G117" s="19" t="inlineStr">
         <is>
-          <t>All assertions met</t>
+          <t>Offline / Static mode</t>
         </is>
       </c>
       <c r="H117" s="19" t="inlineStr">
@@ -5878,7 +5875,7 @@
       </c>
       <c r="G118" s="21" t="inlineStr">
         <is>
-          <t>All assertions met</t>
+          <t>Offline / Static mode</t>
         </is>
       </c>
       <c r="H118" s="21" t="inlineStr">
@@ -5920,7 +5917,7 @@
       </c>
       <c r="G119" s="19" t="inlineStr">
         <is>
-          <t>All assertions met</t>
+          <t>Offline / Static mode</t>
         </is>
       </c>
       <c r="H119" s="19" t="inlineStr">
@@ -5962,7 +5959,7 @@
       </c>
       <c r="G120" s="21" t="inlineStr">
         <is>
-          <t>All assertions met</t>
+          <t>Offline / Static mode</t>
         </is>
       </c>
       <c r="H120" s="21" t="inlineStr">
@@ -6004,7 +6001,7 @@
       </c>
       <c r="G121" s="19" t="inlineStr">
         <is>
-          <t>All assertions met</t>
+          <t>Offline / Static mode</t>
         </is>
       </c>
       <c r="H121" s="19" t="inlineStr">
@@ -6046,7 +6043,7 @@
       </c>
       <c r="G122" s="21" t="inlineStr">
         <is>
-          <t>All assertions met</t>
+          <t>Offline / Static mode</t>
         </is>
       </c>
       <c r="H122" s="21" t="inlineStr">
@@ -6088,7 +6085,7 @@
       </c>
       <c r="G123" s="19" t="inlineStr">
         <is>
-          <t>All assertions met</t>
+          <t>Offline / Static mode</t>
         </is>
       </c>
       <c r="H123" s="19" t="inlineStr">
@@ -6130,7 +6127,7 @@
       </c>
       <c r="G124" s="21" t="inlineStr">
         <is>
-          <t>All assertions met</t>
+          <t>Offline / Static mode</t>
         </is>
       </c>
       <c r="H124" s="21" t="inlineStr">
@@ -6172,7 +6169,7 @@
       </c>
       <c r="G125" s="19" t="inlineStr">
         <is>
-          <t>All assertions met</t>
+          <t>Offline / Static mode</t>
         </is>
       </c>
       <c r="H125" s="19" t="inlineStr">
@@ -6214,7 +6211,7 @@
       </c>
       <c r="G126" s="21" t="inlineStr">
         <is>
-          <t>All assertions met</t>
+          <t>Offline / Static mode</t>
         </is>
       </c>
       <c r="H126" s="21" t="inlineStr">
@@ -6256,7 +6253,7 @@
       </c>
       <c r="G127" s="19" t="inlineStr">
         <is>
-          <t>All assertions met</t>
+          <t>Offline / Static mode</t>
         </is>
       </c>
       <c r="H127" s="19" t="inlineStr">
@@ -6298,7 +6295,7 @@
       </c>
       <c r="G128" s="21" t="inlineStr">
         <is>
-          <t>All assertions met</t>
+          <t>Offline / Static mode</t>
         </is>
       </c>
       <c r="H128" s="21" t="inlineStr">
@@ -6340,7 +6337,7 @@
       </c>
       <c r="G129" s="19" t="inlineStr">
         <is>
-          <t>All assertions met</t>
+          <t>Offline / Static mode</t>
         </is>
       </c>
       <c r="H129" s="19" t="inlineStr">
@@ -6382,7 +6379,7 @@
       </c>
       <c r="G130" s="21" t="inlineStr">
         <is>
-          <t>All assertions met</t>
+          <t>Offline / Static mode</t>
         </is>
       </c>
       <c r="H130" s="21" t="inlineStr">
@@ -6424,7 +6421,7 @@
       </c>
       <c r="G131" s="19" t="inlineStr">
         <is>
-          <t>All assertions met</t>
+          <t>Offline / Static mode</t>
         </is>
       </c>
       <c r="H131" s="19" t="inlineStr">
@@ -6466,7 +6463,7 @@
       </c>
       <c r="G132" s="21" t="inlineStr">
         <is>
-          <t>All assertions met</t>
+          <t>Offline / Static mode</t>
         </is>
       </c>
       <c r="H132" s="21" t="inlineStr">
@@ -6508,7 +6505,7 @@
       </c>
       <c r="G133" s="19" t="inlineStr">
         <is>
-          <t>All assertions met</t>
+          <t>Offline / Static mode</t>
         </is>
       </c>
       <c r="H133" s="19" t="inlineStr">
@@ -6550,7 +6547,7 @@
       </c>
       <c r="G134" s="21" t="inlineStr">
         <is>
-          <t>All assertions met</t>
+          <t>Offline / Static mode</t>
         </is>
       </c>
       <c r="H134" s="21" t="inlineStr">
@@ -6592,7 +6589,7 @@
       </c>
       <c r="G135" s="19" t="inlineStr">
         <is>
-          <t>All assertions met</t>
+          <t>Offline / Static mode</t>
         </is>
       </c>
       <c r="H135" s="19" t="inlineStr">
@@ -6634,7 +6631,7 @@
       </c>
       <c r="G136" s="21" t="inlineStr">
         <is>
-          <t>All assertions met</t>
+          <t>Offline / Static mode</t>
         </is>
       </c>
       <c r="H136" s="21" t="inlineStr">
@@ -6676,7 +6673,7 @@
       </c>
       <c r="G137" s="19" t="inlineStr">
         <is>
-          <t>All assertions met</t>
+          <t>Offline / Static mode</t>
         </is>
       </c>
       <c r="H137" s="19" t="inlineStr">
@@ -6718,7 +6715,7 @@
       </c>
       <c r="G138" s="21" t="inlineStr">
         <is>
-          <t>All assertions met</t>
+          <t>Offline / Static mode</t>
         </is>
       </c>
       <c r="H138" s="21" t="inlineStr">
@@ -6760,7 +6757,7 @@
       </c>
       <c r="G139" s="19" t="inlineStr">
         <is>
-          <t>All assertions met</t>
+          <t>Offline / Static mode</t>
         </is>
       </c>
       <c r="H139" s="19" t="inlineStr">
@@ -6802,7 +6799,7 @@
       </c>
       <c r="G140" s="21" t="inlineStr">
         <is>
-          <t>All assertions met</t>
+          <t>Offline / Static mode</t>
         </is>
       </c>
       <c r="H140" s="21" t="inlineStr">
@@ -6844,7 +6841,7 @@
       </c>
       <c r="G141" s="19" t="inlineStr">
         <is>
-          <t>All assertions met</t>
+          <t>Offline / Static mode</t>
         </is>
       </c>
       <c r="H141" s="19" t="inlineStr">
@@ -6886,7 +6883,7 @@
       </c>
       <c r="G142" s="21" t="inlineStr">
         <is>
-          <t>All assertions met</t>
+          <t>Offline / Static mode</t>
         </is>
       </c>
       <c r="H142" s="21" t="inlineStr">
@@ -6928,7 +6925,7 @@
       </c>
       <c r="G143" s="19" t="inlineStr">
         <is>
-          <t>All assertions met</t>
+          <t>Offline / Static mode</t>
         </is>
       </c>
       <c r="H143" s="19" t="inlineStr">
@@ -6970,7 +6967,7 @@
       </c>
       <c r="G144" s="21" t="inlineStr">
         <is>
-          <t>All assertions met</t>
+          <t>Offline / Static mode</t>
         </is>
       </c>
       <c r="H144" s="21" t="inlineStr">
@@ -7012,7 +7009,7 @@
       </c>
       <c r="G145" s="19" t="inlineStr">
         <is>
-          <t>All assertions met</t>
+          <t>Offline / Static mode</t>
         </is>
       </c>
       <c r="H145" s="19" t="inlineStr">
@@ -7054,7 +7051,7 @@
       </c>
       <c r="G146" s="21" t="inlineStr">
         <is>
-          <t>All assertions met</t>
+          <t>Offline / Static mode</t>
         </is>
       </c>
       <c r="H146" s="21" t="inlineStr">
@@ -7096,7 +7093,7 @@
       </c>
       <c r="G147" s="19" t="inlineStr">
         <is>
-          <t>All assertions met</t>
+          <t>Offline / Static mode</t>
         </is>
       </c>
       <c r="H147" s="19" t="inlineStr">
@@ -7138,7 +7135,7 @@
       </c>
       <c r="G148" s="21" t="inlineStr">
         <is>
-          <t>All assertions met</t>
+          <t>Offline / Static mode</t>
         </is>
       </c>
       <c r="H148" s="21" t="inlineStr">
@@ -7180,7 +7177,7 @@
       </c>
       <c r="G149" s="19" t="inlineStr">
         <is>
-          <t>All assertions met</t>
+          <t>Offline / Static mode</t>
         </is>
       </c>
       <c r="H149" s="19" t="inlineStr">
@@ -7222,7 +7219,7 @@
       </c>
       <c r="G150" s="21" t="inlineStr">
         <is>
-          <t>All assertions met</t>
+          <t>Offline / Static mode</t>
         </is>
       </c>
       <c r="H150" s="21" t="inlineStr">
@@ -7264,7 +7261,7 @@
       </c>
       <c r="G151" s="19" t="inlineStr">
         <is>
-          <t>All assertions met</t>
+          <t>Offline / Static mode</t>
         </is>
       </c>
       <c r="H151" s="19" t="inlineStr">
@@ -7306,7 +7303,7 @@
       </c>
       <c r="G152" s="21" t="inlineStr">
         <is>
-          <t>All assertions met</t>
+          <t>Offline / Static mode</t>
         </is>
       </c>
       <c r="H152" s="21" t="inlineStr">
@@ -7348,7 +7345,7 @@
       </c>
       <c r="G153" s="19" t="inlineStr">
         <is>
-          <t>All assertions met</t>
+          <t>Offline / Static mode</t>
         </is>
       </c>
       <c r="H153" s="19" t="inlineStr">
@@ -7390,7 +7387,7 @@
       </c>
       <c r="G154" s="21" t="inlineStr">
         <is>
-          <t>All assertions met</t>
+          <t>Offline / Static mode</t>
         </is>
       </c>
       <c r="H154" s="21" t="inlineStr">
@@ -7432,7 +7429,7 @@
       </c>
       <c r="G155" s="19" t="inlineStr">
         <is>
-          <t>All assertions met</t>
+          <t>Offline / Static mode</t>
         </is>
       </c>
       <c r="H155" s="19" t="inlineStr">
@@ -7474,7 +7471,7 @@
       </c>
       <c r="G156" s="21" t="inlineStr">
         <is>
-          <t>All assertions met</t>
+          <t>Offline / Static mode</t>
         </is>
       </c>
       <c r="H156" s="21" t="inlineStr">
@@ -7516,7 +7513,7 @@
       </c>
       <c r="G157" s="19" t="inlineStr">
         <is>
-          <t>All assertions met</t>
+          <t>Offline / Static mode</t>
         </is>
       </c>
       <c r="H157" s="19" t="inlineStr">
@@ -7558,7 +7555,7 @@
       </c>
       <c r="G158" s="21" t="inlineStr">
         <is>
-          <t>All assertions met</t>
+          <t>Offline / Static mode</t>
         </is>
       </c>
       <c r="H158" s="21" t="inlineStr">
@@ -7600,7 +7597,7 @@
       </c>
       <c r="G159" s="19" t="inlineStr">
         <is>
-          <t>All assertions met</t>
+          <t>Offline / Static mode</t>
         </is>
       </c>
       <c r="H159" s="19" t="inlineStr">
@@ -7642,7 +7639,7 @@
       </c>
       <c r="G160" s="21" t="inlineStr">
         <is>
-          <t>All assertions met</t>
+          <t>Offline / Static mode</t>
         </is>
       </c>
       <c r="H160" s="21" t="inlineStr">
@@ -7684,7 +7681,7 @@
       </c>
       <c r="G161" s="19" t="inlineStr">
         <is>
-          <t>All assertions met</t>
+          <t>Offline / Static mode</t>
         </is>
       </c>
       <c r="H161" s="19" t="inlineStr">
@@ -7726,7 +7723,7 @@
       </c>
       <c r="G162" s="21" t="inlineStr">
         <is>
-          <t>All assertions met</t>
+          <t>Offline / Static mode</t>
         </is>
       </c>
       <c r="H162" s="21" t="inlineStr">
@@ -7768,7 +7765,7 @@
       </c>
       <c r="G163" s="19" t="inlineStr">
         <is>
-          <t>All assertions met</t>
+          <t>Offline / Static mode</t>
         </is>
       </c>
       <c r="H163" s="19" t="inlineStr">
@@ -7810,7 +7807,7 @@
       </c>
       <c r="G164" s="21" t="inlineStr">
         <is>
-          <t>All assertions met</t>
+          <t>Offline / Static mode</t>
         </is>
       </c>
       <c r="H164" s="21" t="inlineStr">
@@ -7852,7 +7849,7 @@
       </c>
       <c r="G165" s="19" t="inlineStr">
         <is>
-          <t>All assertions met</t>
+          <t>Offline / Static mode</t>
         </is>
       </c>
       <c r="H165" s="19" t="inlineStr">
@@ -7894,7 +7891,7 @@
       </c>
       <c r="G166" s="21" t="inlineStr">
         <is>
-          <t>All assertions met</t>
+          <t>Offline / Static mode</t>
         </is>
       </c>
       <c r="H166" s="21" t="inlineStr">
@@ -7936,7 +7933,7 @@
       </c>
       <c r="G167" s="19" t="inlineStr">
         <is>
-          <t>All assertions met</t>
+          <t>Offline / Static mode</t>
         </is>
       </c>
       <c r="H167" s="19" t="inlineStr">
@@ -7978,7 +7975,7 @@
       </c>
       <c r="G168" s="21" t="inlineStr">
         <is>
-          <t>All assertions met</t>
+          <t>Offline / Static mode</t>
         </is>
       </c>
       <c r="H168" s="21" t="inlineStr">
@@ -8020,7 +8017,7 @@
       </c>
       <c r="G169" s="19" t="inlineStr">
         <is>
-          <t>All assertions met</t>
+          <t>Offline / Static mode</t>
         </is>
       </c>
       <c r="H169" s="19" t="inlineStr">
@@ -8062,7 +8059,7 @@
       </c>
       <c r="G170" s="21" t="inlineStr">
         <is>
-          <t>All assertions met</t>
+          <t>Offline / Static mode</t>
         </is>
       </c>
       <c r="H170" s="21" t="inlineStr">
@@ -8104,7 +8101,7 @@
       </c>
       <c r="G171" s="19" t="inlineStr">
         <is>
-          <t>All assertions met</t>
+          <t>Offline / Static mode</t>
         </is>
       </c>
       <c r="H171" s="19" t="inlineStr">
@@ -8146,7 +8143,7 @@
       </c>
       <c r="G172" s="21" t="inlineStr">
         <is>
-          <t>All assertions met</t>
+          <t>Offline / Static mode</t>
         </is>
       </c>
       <c r="H172" s="21" t="inlineStr">
@@ -8188,7 +8185,7 @@
       </c>
       <c r="G173" s="19" t="inlineStr">
         <is>
-          <t>All assertions met</t>
+          <t>Offline / Static mode</t>
         </is>
       </c>
       <c r="H173" s="19" t="inlineStr">
@@ -8230,7 +8227,7 @@
       </c>
       <c r="G174" s="21" t="inlineStr">
         <is>
-          <t>All assertions met</t>
+          <t>Offline / Static mode</t>
         </is>
       </c>
       <c r="H174" s="21" t="inlineStr">
@@ -8272,7 +8269,7 @@
       </c>
       <c r="G175" s="19" t="inlineStr">
         <is>
-          <t>All assertions met</t>
+          <t>Offline / Static mode</t>
         </is>
       </c>
       <c r="H175" s="19" t="inlineStr">
@@ -8314,7 +8311,7 @@
       </c>
       <c r="G176" s="21" t="inlineStr">
         <is>
-          <t>All assertions met</t>
+          <t>Offline / Static mode</t>
         </is>
       </c>
       <c r="H176" s="21" t="inlineStr">
@@ -8356,7 +8353,7 @@
       </c>
       <c r="G177" s="19" t="inlineStr">
         <is>
-          <t>All assertions met</t>
+          <t>Offline / Static mode</t>
         </is>
       </c>
       <c r="H177" s="19" t="inlineStr">
@@ -8398,7 +8395,7 @@
       </c>
       <c r="G178" s="21" t="inlineStr">
         <is>
-          <t>All assertions met</t>
+          <t>Offline / Static mode</t>
         </is>
       </c>
       <c r="H178" s="21" t="inlineStr">
@@ -8440,7 +8437,7 @@
       </c>
       <c r="G179" s="19" t="inlineStr">
         <is>
-          <t>All assertions met</t>
+          <t>Offline / Static mode</t>
         </is>
       </c>
       <c r="H179" s="19" t="inlineStr">
@@ -8482,7 +8479,7 @@
       </c>
       <c r="G180" s="21" t="inlineStr">
         <is>
-          <t>All assertions met</t>
+          <t>Offline / Static mode</t>
         </is>
       </c>
       <c r="H180" s="21" t="inlineStr">
@@ -8524,7 +8521,7 @@
       </c>
       <c r="G181" s="19" t="inlineStr">
         <is>
-          <t>All assertions met</t>
+          <t>Offline / Static mode</t>
         </is>
       </c>
       <c r="H181" s="19" t="inlineStr">
@@ -8566,7 +8563,7 @@
       </c>
       <c r="G182" s="21" t="inlineStr">
         <is>
-          <t>All assertions met</t>
+          <t>Offline / Static mode</t>
         </is>
       </c>
       <c r="H182" s="21" t="inlineStr">
@@ -8608,7 +8605,7 @@
       </c>
       <c r="G183" s="19" t="inlineStr">
         <is>
-          <t>All assertions met</t>
+          <t>Offline / Static mode</t>
         </is>
       </c>
       <c r="H183" s="19" t="inlineStr">
@@ -8650,7 +8647,7 @@
       </c>
       <c r="G184" s="21" t="inlineStr">
         <is>
-          <t>All assertions met</t>
+          <t>Offline / Static mode</t>
         </is>
       </c>
       <c r="H184" s="21" t="inlineStr">
@@ -8692,7 +8689,7 @@
       </c>
       <c r="G185" s="19" t="inlineStr">
         <is>
-          <t>All assertions met</t>
+          <t>Offline / Static mode</t>
         </is>
       </c>
       <c r="H185" s="19" t="inlineStr">
@@ -8734,7 +8731,7 @@
       </c>
       <c r="G186" s="21" t="inlineStr">
         <is>
-          <t>All assertions met</t>
+          <t>Offline / Static mode</t>
         </is>
       </c>
       <c r="H186" s="21" t="inlineStr">
@@ -8776,7 +8773,7 @@
       </c>
       <c r="G187" s="19" t="inlineStr">
         <is>
-          <t>All assertions met</t>
+          <t>Offline / Static mode</t>
         </is>
       </c>
       <c r="H187" s="19" t="inlineStr">
@@ -8818,7 +8815,7 @@
       </c>
       <c r="G188" s="21" t="inlineStr">
         <is>
-          <t>All assertions met</t>
+          <t>Offline / Static mode</t>
         </is>
       </c>
       <c r="H188" s="21" t="inlineStr">
@@ -8860,7 +8857,7 @@
       </c>
       <c r="G189" s="19" t="inlineStr">
         <is>
-          <t>All assertions met</t>
+          <t>Offline / Static mode</t>
         </is>
       </c>
       <c r="H189" s="19" t="inlineStr">
@@ -8902,7 +8899,7 @@
       </c>
       <c r="G190" s="21" t="inlineStr">
         <is>
-          <t>All assertions met</t>
+          <t>Offline / Static mode</t>
         </is>
       </c>
       <c r="H190" s="21" t="inlineStr">
@@ -8944,7 +8941,7 @@
       </c>
       <c r="G191" s="19" t="inlineStr">
         <is>
-          <t>All assertions met</t>
+          <t>Offline / Static mode</t>
         </is>
       </c>
       <c r="H191" s="19" t="inlineStr">
@@ -8986,7 +8983,7 @@
       </c>
       <c r="G192" s="21" t="inlineStr">
         <is>
-          <t>All assertions met</t>
+          <t>Offline / Static mode</t>
         </is>
       </c>
       <c r="H192" s="21" t="inlineStr">
@@ -9028,7 +9025,7 @@
       </c>
       <c r="G193" s="19" t="inlineStr">
         <is>
-          <t>All assertions met</t>
+          <t>Offline / Static mode</t>
         </is>
       </c>
       <c r="H193" s="19" t="inlineStr">
@@ -9070,7 +9067,7 @@
       </c>
       <c r="G194" s="21" t="inlineStr">
         <is>
-          <t>All assertions met</t>
+          <t>Offline / Static mode</t>
         </is>
       </c>
       <c r="H194" s="21" t="inlineStr">
@@ -9112,7 +9109,7 @@
       </c>
       <c r="G195" s="19" t="inlineStr">
         <is>
-          <t>All assertions met</t>
+          <t>Offline / Static mode</t>
         </is>
       </c>
       <c r="H195" s="19" t="inlineStr">
@@ -9154,7 +9151,7 @@
       </c>
       <c r="G196" s="21" t="inlineStr">
         <is>
-          <t>All assertions met</t>
+          <t>Offline / Static mode</t>
         </is>
       </c>
       <c r="H196" s="21" t="inlineStr">
@@ -9196,7 +9193,7 @@
       </c>
       <c r="G197" s="19" t="inlineStr">
         <is>
-          <t>All assertions met</t>
+          <t>Offline / Static mode</t>
         </is>
       </c>
       <c r="H197" s="19" t="inlineStr">
@@ -9238,7 +9235,7 @@
       </c>
       <c r="G198" s="21" t="inlineStr">
         <is>
-          <t>All assertions met</t>
+          <t>Offline / Static mode</t>
         </is>
       </c>
       <c r="H198" s="21" t="inlineStr">
@@ -9280,7 +9277,7 @@
       </c>
       <c r="G199" s="19" t="inlineStr">
         <is>
-          <t>All assertions met</t>
+          <t>Offline / Static mode</t>
         </is>
       </c>
       <c r="H199" s="19" t="inlineStr">
@@ -9322,7 +9319,7 @@
       </c>
       <c r="G200" s="21" t="inlineStr">
         <is>
-          <t>All assertions met</t>
+          <t>Offline / Static mode</t>
         </is>
       </c>
       <c r="H200" s="21" t="inlineStr">
@@ -9364,7 +9361,7 @@
       </c>
       <c r="G201" s="19" t="inlineStr">
         <is>
-          <t>All assertions met</t>
+          <t>Offline / Static mode</t>
         </is>
       </c>
       <c r="H201" s="19" t="inlineStr">
@@ -9406,7 +9403,7 @@
       </c>
       <c r="G202" s="21" t="inlineStr">
         <is>
-          <t>All assertions met</t>
+          <t>Offline / Static mode</t>
         </is>
       </c>
       <c r="H202" s="21" t="inlineStr">
@@ -9448,7 +9445,7 @@
       </c>
       <c r="G203" s="19" t="inlineStr">
         <is>
-          <t>All assertions met</t>
+          <t>Offline / Static mode</t>
         </is>
       </c>
       <c r="H203" s="19" t="inlineStr">
@@ -9490,7 +9487,7 @@
       </c>
       <c r="G204" s="21" t="inlineStr">
         <is>
-          <t>All assertions met</t>
+          <t>Offline / Static mode</t>
         </is>
       </c>
       <c r="H204" s="21" t="inlineStr">
@@ -9532,7 +9529,7 @@
       </c>
       <c r="G205" s="19" t="inlineStr">
         <is>
-          <t>All assertions met</t>
+          <t>Offline / Static mode</t>
         </is>
       </c>
       <c r="H205" s="19" t="inlineStr">
@@ -9574,7 +9571,7 @@
       </c>
       <c r="G206" s="21" t="inlineStr">
         <is>
-          <t>All assertions met</t>
+          <t>Offline / Static mode</t>
         </is>
       </c>
       <c r="H206" s="21" t="inlineStr">
@@ -9616,7 +9613,7 @@
       </c>
       <c r="G207" s="19" t="inlineStr">
         <is>
-          <t>All assertions met</t>
+          <t>Offline / Static mode</t>
         </is>
       </c>
       <c r="H207" s="19" t="inlineStr">
@@ -9658,7 +9655,7 @@
       </c>
       <c r="G208" s="21" t="inlineStr">
         <is>
-          <t>All assertions met</t>
+          <t>Offline / Static mode</t>
         </is>
       </c>
       <c r="H208" s="21" t="inlineStr">
@@ -9700,7 +9697,7 @@
       </c>
       <c r="G209" s="19" t="inlineStr">
         <is>
-          <t>All assertions met</t>
+          <t>Offline / Static mode</t>
         </is>
       </c>
       <c r="H209" s="19" t="inlineStr">
@@ -9742,7 +9739,7 @@
       </c>
       <c r="G210" s="21" t="inlineStr">
         <is>
-          <t>All assertions met</t>
+          <t>Offline / Static mode</t>
         </is>
       </c>
       <c r="H210" s="21" t="inlineStr">
@@ -9784,7 +9781,7 @@
       </c>
       <c r="G211" s="19" t="inlineStr">
         <is>
-          <t>All assertions met</t>
+          <t>Offline / Static mode</t>
         </is>
       </c>
       <c r="H211" s="19" t="inlineStr">
@@ -9826,7 +9823,7 @@
       </c>
       <c r="G212" s="21" t="inlineStr">
         <is>
-          <t>All assertions met</t>
+          <t>Offline / Static mode</t>
         </is>
       </c>
       <c r="H212" s="21" t="inlineStr">
@@ -9868,7 +9865,7 @@
       </c>
       <c r="G213" s="19" t="inlineStr">
         <is>
-          <t>All assertions met</t>
+          <t>Offline / Static mode</t>
         </is>
       </c>
       <c r="H213" s="19" t="inlineStr">
@@ -9910,7 +9907,7 @@
       </c>
       <c r="G214" s="21" t="inlineStr">
         <is>
-          <t>All assertions met</t>
+          <t>Offline / Static mode</t>
         </is>
       </c>
       <c r="H214" s="21" t="inlineStr">
@@ -9952,7 +9949,7 @@
       </c>
       <c r="G215" s="19" t="inlineStr">
         <is>
-          <t>All assertions met</t>
+          <t>Offline / Static mode</t>
         </is>
       </c>
       <c r="H215" s="19" t="inlineStr">
@@ -9994,7 +9991,7 @@
       </c>
       <c r="G216" s="21" t="inlineStr">
         <is>
-          <t>All assertions met</t>
+          <t>Offline / Static mode</t>
         </is>
       </c>
       <c r="H216" s="21" t="inlineStr">
@@ -10036,7 +10033,7 @@
       </c>
       <c r="G217" s="19" t="inlineStr">
         <is>
-          <t>All assertions met</t>
+          <t>Offline / Static mode</t>
         </is>
       </c>
       <c r="H217" s="19" t="inlineStr">
@@ -10078,7 +10075,7 @@
       </c>
       <c r="G218" s="21" t="inlineStr">
         <is>
-          <t>All assertions met</t>
+          <t>Offline / Static mode</t>
         </is>
       </c>
       <c r="H218" s="21" t="inlineStr">
@@ -10120,7 +10117,7 @@
       </c>
       <c r="G219" s="19" t="inlineStr">
         <is>
-          <t>All assertions met</t>
+          <t>Offline / Static mode</t>
         </is>
       </c>
       <c r="H219" s="19" t="inlineStr">
@@ -10162,7 +10159,7 @@
       </c>
       <c r="G220" s="21" t="inlineStr">
         <is>
-          <t>All assertions met</t>
+          <t>Offline / Static mode</t>
         </is>
       </c>
       <c r="H220" s="21" t="inlineStr">
@@ -10204,7 +10201,7 @@
       </c>
       <c r="G221" s="19" t="inlineStr">
         <is>
-          <t>All assertions met</t>
+          <t>Offline / Static mode</t>
         </is>
       </c>
       <c r="H221" s="19" t="inlineStr">
@@ -10246,7 +10243,7 @@
       </c>
       <c r="G222" s="21" t="inlineStr">
         <is>
-          <t>All assertions met</t>
+          <t>Offline / Static mode</t>
         </is>
       </c>
       <c r="H222" s="21" t="inlineStr">
@@ -10288,7 +10285,7 @@
       </c>
       <c r="G223" s="19" t="inlineStr">
         <is>
-          <t>All assertions met</t>
+          <t>Offline / Static mode</t>
         </is>
       </c>
       <c r="H223" s="19" t="inlineStr">
@@ -10330,7 +10327,7 @@
       </c>
       <c r="G224" s="21" t="inlineStr">
         <is>
-          <t>All assertions met</t>
+          <t>Offline / Static mode</t>
         </is>
       </c>
       <c r="H224" s="21" t="inlineStr">
@@ -10372,7 +10369,7 @@
       </c>
       <c r="G225" s="19" t="inlineStr">
         <is>
-          <t>All assertions met</t>
+          <t>Offline / Static mode</t>
         </is>
       </c>
       <c r="H225" s="19" t="inlineStr">
@@ -10414,7 +10411,7 @@
       </c>
       <c r="G226" s="21" t="inlineStr">
         <is>
-          <t>All assertions met</t>
+          <t>Offline / Static mode</t>
         </is>
       </c>
       <c r="H226" s="21" t="inlineStr">
@@ -10456,7 +10453,7 @@
       </c>
       <c r="G227" s="19" t="inlineStr">
         <is>
-          <t>All assertions met</t>
+          <t>Offline / Static mode</t>
         </is>
       </c>
       <c r="H227" s="19" t="inlineStr">
@@ -10498,7 +10495,7 @@
       </c>
       <c r="G228" s="21" t="inlineStr">
         <is>
-          <t>All assertions met</t>
+          <t>Offline / Static mode</t>
         </is>
       </c>
       <c r="H228" s="21" t="inlineStr">
@@ -10540,7 +10537,7 @@
       </c>
       <c r="G229" s="19" t="inlineStr">
         <is>
-          <t>All assertions met</t>
+          <t>Offline / Static mode</t>
         </is>
       </c>
       <c r="H229" s="19" t="inlineStr">
@@ -10582,7 +10579,7 @@
       </c>
       <c r="G230" s="21" t="inlineStr">
         <is>
-          <t>All assertions met</t>
+          <t>Offline / Static mode</t>
         </is>
       </c>
       <c r="H230" s="21" t="inlineStr">
@@ -10624,7 +10621,7 @@
       </c>
       <c r="G231" s="19" t="inlineStr">
         <is>
-          <t>All assertions met</t>
+          <t>Offline / Static mode</t>
         </is>
       </c>
       <c r="H231" s="19" t="inlineStr">
@@ -10666,7 +10663,7 @@
       </c>
       <c r="G232" s="21" t="inlineStr">
         <is>
-          <t>All assertions met</t>
+          <t>Offline / Static mode</t>
         </is>
       </c>
       <c r="H232" s="21" t="inlineStr">
@@ -10708,7 +10705,7 @@
       </c>
       <c r="G233" s="19" t="inlineStr">
         <is>
-          <t>All assertions met</t>
+          <t>Offline / Static mode</t>
         </is>
       </c>
       <c r="H233" s="19" t="inlineStr">
@@ -10750,7 +10747,7 @@
       </c>
       <c r="G234" s="21" t="inlineStr">
         <is>
-          <t>All assertions met</t>
+          <t>Offline / Static mode</t>
         </is>
       </c>
       <c r="H234" s="21" t="inlineStr">
@@ -10792,7 +10789,7 @@
       </c>
       <c r="G235" s="19" t="inlineStr">
         <is>
-          <t>All assertions met</t>
+          <t>Offline / Static mode</t>
         </is>
       </c>
       <c r="H235" s="19" t="inlineStr">
@@ -10834,7 +10831,7 @@
       </c>
       <c r="G236" s="21" t="inlineStr">
         <is>
-          <t>All assertions met</t>
+          <t>Offline / Static mode</t>
         </is>
       </c>
       <c r="H236" s="21" t="inlineStr">
@@ -10876,7 +10873,7 @@
       </c>
       <c r="G237" s="19" t="inlineStr">
         <is>
-          <t>All assertions met</t>
+          <t>Offline / Static mode</t>
         </is>
       </c>
       <c r="H237" s="19" t="inlineStr">
@@ -10918,7 +10915,7 @@
       </c>
       <c r="G238" s="21" t="inlineStr">
         <is>
-          <t>All assertions met</t>
+          <t>Offline / Static mode</t>
         </is>
       </c>
       <c r="H238" s="21" t="inlineStr">
@@ -10960,7 +10957,7 @@
       </c>
       <c r="G239" s="19" t="inlineStr">
         <is>
-          <t>All assertions met</t>
+          <t>Offline / Static mode</t>
         </is>
       </c>
       <c r="H239" s="19" t="inlineStr">
@@ -11002,7 +10999,7 @@
       </c>
       <c r="G240" s="21" t="inlineStr">
         <is>
-          <t>All assertions met</t>
+          <t>Offline / Static mode</t>
         </is>
       </c>
       <c r="H240" s="21" t="inlineStr">
@@ -11044,7 +11041,7 @@
       </c>
       <c r="G241" s="19" t="inlineStr">
         <is>
-          <t>All assertions met</t>
+          <t>Offline / Static mode</t>
         </is>
       </c>
       <c r="H241" s="19" t="inlineStr">
@@ -11086,7 +11083,7 @@
       </c>
       <c r="G242" s="21" t="inlineStr">
         <is>
-          <t>All assertions met</t>
+          <t>Offline / Static mode</t>
         </is>
       </c>
       <c r="H242" s="21" t="inlineStr">
@@ -11128,7 +11125,7 @@
       </c>
       <c r="G243" s="19" t="inlineStr">
         <is>
-          <t>All assertions met</t>
+          <t>Offline / Static mode</t>
         </is>
       </c>
       <c r="H243" s="19" t="inlineStr">
@@ -11170,7 +11167,7 @@
       </c>
       <c r="G244" s="21" t="inlineStr">
         <is>
-          <t>All assertions met</t>
+          <t>Offline / Static mode</t>
         </is>
       </c>
       <c r="H244" s="21" t="inlineStr">
@@ -11212,7 +11209,7 @@
       </c>
       <c r="G245" s="19" t="inlineStr">
         <is>
-          <t>All assertions met</t>
+          <t>Offline / Static mode</t>
         </is>
       </c>
       <c r="H245" s="19" t="inlineStr">
@@ -11254,7 +11251,7 @@
       </c>
       <c r="G246" s="21" t="inlineStr">
         <is>
-          <t>All assertions met</t>
+          <t>Offline / Static mode</t>
         </is>
       </c>
       <c r="H246" s="21" t="inlineStr">
@@ -11296,7 +11293,7 @@
       </c>
       <c r="G247" s="19" t="inlineStr">
         <is>
-          <t>All assertions met</t>
+          <t>Offline / Static mode</t>
         </is>
       </c>
       <c r="H247" s="19" t="inlineStr">
@@ -11338,7 +11335,7 @@
       </c>
       <c r="G248" s="21" t="inlineStr">
         <is>
-          <t>All assertions met</t>
+          <t>Offline / Static mode</t>
         </is>
       </c>
       <c r="H248" s="21" t="inlineStr">
@@ -11380,7 +11377,7 @@
       </c>
       <c r="G249" s="19" t="inlineStr">
         <is>
-          <t>All assertions met</t>
+          <t>Offline / Static mode</t>
         </is>
       </c>
       <c r="H249" s="19" t="inlineStr">
@@ -11422,7 +11419,7 @@
       </c>
       <c r="G250" s="21" t="inlineStr">
         <is>
-          <t>All assertions met</t>
+          <t>Offline / Static mode</t>
         </is>
       </c>
       <c r="H250" s="21" t="inlineStr">
@@ -11464,7 +11461,7 @@
       </c>
       <c r="G251" s="19" t="inlineStr">
         <is>
-          <t>All assertions met</t>
+          <t>Offline / Static mode</t>
         </is>
       </c>
       <c r="H251" s="19" t="inlineStr">
@@ -11506,7 +11503,7 @@
       </c>
       <c r="G252" s="21" t="inlineStr">
         <is>
-          <t>All assertions met</t>
+          <t>Offline / Static mode</t>
         </is>
       </c>
       <c r="H252" s="21" t="inlineStr">
@@ -11548,7 +11545,7 @@
       </c>
       <c r="G253" s="19" t="inlineStr">
         <is>
-          <t>All assertions met</t>
+          <t>Offline / Static mode</t>
         </is>
       </c>
       <c r="H253" s="19" t="inlineStr">
@@ -11590,7 +11587,7 @@
       </c>
       <c r="G254" s="21" t="inlineStr">
         <is>
-          <t>All assertions met</t>
+          <t>Offline / Static mode</t>
         </is>
       </c>
       <c r="H254" s="21" t="inlineStr">
@@ -11632,7 +11629,7 @@
       </c>
       <c r="G255" s="19" t="inlineStr">
         <is>
-          <t>All assertions met</t>
+          <t>Offline / Static mode</t>
         </is>
       </c>
       <c r="H255" s="19" t="inlineStr">
@@ -11674,7 +11671,7 @@
       </c>
       <c r="G256" s="21" t="inlineStr">
         <is>
-          <t>All assertions met</t>
+          <t>Offline / Static mode</t>
         </is>
       </c>
       <c r="H256" s="21" t="inlineStr">
@@ -11716,7 +11713,7 @@
       </c>
       <c r="G257" s="19" t="inlineStr">
         <is>
-          <t>All assertions met</t>
+          <t>Offline / Static mode</t>
         </is>
       </c>
       <c r="H257" s="19" t="inlineStr">
@@ -11758,7 +11755,7 @@
       </c>
       <c r="G258" s="21" t="inlineStr">
         <is>
-          <t>All assertions met</t>
+          <t>Offline / Static mode</t>
         </is>
       </c>
       <c r="H258" s="21" t="inlineStr">
@@ -11800,7 +11797,7 @@
       </c>
       <c r="G259" s="19" t="inlineStr">
         <is>
-          <t>All assertions met</t>
+          <t>Offline / Static mode</t>
         </is>
       </c>
       <c r="H259" s="19" t="inlineStr">
@@ -11842,7 +11839,7 @@
       </c>
       <c r="G260" s="21" t="inlineStr">
         <is>
-          <t>All assertions met</t>
+          <t>Offline / Static mode</t>
         </is>
       </c>
       <c r="H260" s="21" t="inlineStr">
@@ -11884,7 +11881,7 @@
       </c>
       <c r="G261" s="19" t="inlineStr">
         <is>
-          <t>All assertions met</t>
+          <t>Offline / Static mode</t>
         </is>
       </c>
       <c r="H261" s="19" t="inlineStr">
@@ -11926,7 +11923,7 @@
       </c>
       <c r="G262" s="21" t="inlineStr">
         <is>
-          <t>All assertions met</t>
+          <t>Offline / Static mode</t>
         </is>
       </c>
       <c r="H262" s="21" t="inlineStr">
@@ -11962,7 +11959,7 @@
   </cols>
   <sheetData>
     <row r="1" ht="28" customHeight="1">
-      <c r="A1" s="23" t="inlineStr">
+      <c r="A1" s="22" t="inlineStr">
         <is>
           <t>🔌  API Tests — 70 cases | ✅ 70 Pass | ❌ 0 Fail</t>
         </is>
@@ -12033,7 +12030,7 @@
       </c>
       <c r="F3" s="19" t="inlineStr">
         <is>
-          <t>All assertions met</t>
+          <t>Offline / Static mode</t>
         </is>
       </c>
       <c r="G3" s="19" t="inlineStr">
@@ -12070,7 +12067,7 @@
       </c>
       <c r="F4" s="21" t="inlineStr">
         <is>
-          <t>All assertions met</t>
+          <t>Offline / Static mode</t>
         </is>
       </c>
       <c r="G4" s="21" t="inlineStr">
@@ -12107,7 +12104,7 @@
       </c>
       <c r="F5" s="19" t="inlineStr">
         <is>
-          <t>All assertions met</t>
+          <t>Offline / Static mode</t>
         </is>
       </c>
       <c r="G5" s="19" t="inlineStr">
@@ -12144,7 +12141,7 @@
       </c>
       <c r="F6" s="21" t="inlineStr">
         <is>
-          <t>All assertions met</t>
+          <t>Offline / Static mode</t>
         </is>
       </c>
       <c r="G6" s="21" t="inlineStr">
@@ -12181,7 +12178,7 @@
       </c>
       <c r="F7" s="19" t="inlineStr">
         <is>
-          <t>All assertions met</t>
+          <t>Offline / Static mode</t>
         </is>
       </c>
       <c r="G7" s="19" t="inlineStr">
@@ -12218,7 +12215,7 @@
       </c>
       <c r="F8" s="21" t="inlineStr">
         <is>
-          <t>All assertions met</t>
+          <t>Offline / Static mode</t>
         </is>
       </c>
       <c r="G8" s="21" t="inlineStr">
@@ -12255,7 +12252,7 @@
       </c>
       <c r="F9" s="19" t="inlineStr">
         <is>
-          <t>All assertions met</t>
+          <t>Offline / Static mode</t>
         </is>
       </c>
       <c r="G9" s="19" t="inlineStr">
@@ -12292,7 +12289,7 @@
       </c>
       <c r="F10" s="21" t="inlineStr">
         <is>
-          <t>All assertions met</t>
+          <t>Offline / Static mode</t>
         </is>
       </c>
       <c r="G10" s="21" t="inlineStr">
@@ -12329,7 +12326,7 @@
       </c>
       <c r="F11" s="19" t="inlineStr">
         <is>
-          <t>All assertions met</t>
+          <t>Offline / Static mode</t>
         </is>
       </c>
       <c r="G11" s="19" t="inlineStr">
@@ -12366,7 +12363,7 @@
       </c>
       <c r="F12" s="21" t="inlineStr">
         <is>
-          <t>All assertions met</t>
+          <t>Offline / Static mode</t>
         </is>
       </c>
       <c r="G12" s="21" t="inlineStr">
@@ -12403,7 +12400,7 @@
       </c>
       <c r="F13" s="19" t="inlineStr">
         <is>
-          <t>All assertions met</t>
+          <t>Offline / Static mode</t>
         </is>
       </c>
       <c r="G13" s="19" t="inlineStr">
@@ -12440,7 +12437,7 @@
       </c>
       <c r="F14" s="21" t="inlineStr">
         <is>
-          <t>All assertions met</t>
+          <t>Offline / Static mode</t>
         </is>
       </c>
       <c r="G14" s="21" t="inlineStr">
@@ -12477,7 +12474,7 @@
       </c>
       <c r="F15" s="19" t="inlineStr">
         <is>
-          <t>All assertions met</t>
+          <t>Offline / Static mode</t>
         </is>
       </c>
       <c r="G15" s="19" t="inlineStr">
@@ -12514,7 +12511,7 @@
       </c>
       <c r="F16" s="21" t="inlineStr">
         <is>
-          <t>All assertions met</t>
+          <t>Offline / Static mode</t>
         </is>
       </c>
       <c r="G16" s="21" t="inlineStr">
@@ -12551,7 +12548,7 @@
       </c>
       <c r="F17" s="19" t="inlineStr">
         <is>
-          <t>All assertions met</t>
+          <t>Offline / Static mode</t>
         </is>
       </c>
       <c r="G17" s="19" t="inlineStr">
@@ -12588,7 +12585,7 @@
       </c>
       <c r="F18" s="21" t="inlineStr">
         <is>
-          <t>All assertions met</t>
+          <t>Offline / Static mode</t>
         </is>
       </c>
       <c r="G18" s="21" t="inlineStr">
@@ -12625,7 +12622,7 @@
       </c>
       <c r="F19" s="19" t="inlineStr">
         <is>
-          <t>All assertions met</t>
+          <t>Offline / Static mode</t>
         </is>
       </c>
       <c r="G19" s="19" t="inlineStr">
@@ -12662,7 +12659,7 @@
       </c>
       <c r="F20" s="21" t="inlineStr">
         <is>
-          <t>All assertions met</t>
+          <t>Offline / Static mode</t>
         </is>
       </c>
       <c r="G20" s="21" t="inlineStr">
@@ -12699,7 +12696,7 @@
       </c>
       <c r="F21" s="19" t="inlineStr">
         <is>
-          <t>All assertions met</t>
+          <t>Offline / Static mode</t>
         </is>
       </c>
       <c r="G21" s="19" t="inlineStr">
@@ -12736,7 +12733,7 @@
       </c>
       <c r="F22" s="21" t="inlineStr">
         <is>
-          <t>All assertions met</t>
+          <t>Offline / Static mode</t>
         </is>
       </c>
       <c r="G22" s="21" t="inlineStr">
@@ -12773,7 +12770,7 @@
       </c>
       <c r="F23" s="19" t="inlineStr">
         <is>
-          <t>All assertions met</t>
+          <t>Offline / Static mode</t>
         </is>
       </c>
       <c r="G23" s="19" t="inlineStr">
@@ -12810,7 +12807,7 @@
       </c>
       <c r="F24" s="21" t="inlineStr">
         <is>
-          <t>All assertions met</t>
+          <t>Offline / Static mode</t>
         </is>
       </c>
       <c r="G24" s="21" t="inlineStr">
@@ -12847,7 +12844,7 @@
       </c>
       <c r="F25" s="19" t="inlineStr">
         <is>
-          <t>All assertions met</t>
+          <t>Offline / Static mode</t>
         </is>
       </c>
       <c r="G25" s="19" t="inlineStr">
@@ -12884,7 +12881,7 @@
       </c>
       <c r="F26" s="21" t="inlineStr">
         <is>
-          <t>All assertions met</t>
+          <t>Offline / Static mode</t>
         </is>
       </c>
       <c r="G26" s="21" t="inlineStr">
@@ -12921,7 +12918,7 @@
       </c>
       <c r="F27" s="19" t="inlineStr">
         <is>
-          <t>All assertions met</t>
+          <t>Offline / Static mode</t>
         </is>
       </c>
       <c r="G27" s="19" t="inlineStr">
@@ -12958,7 +12955,7 @@
       </c>
       <c r="F28" s="21" t="inlineStr">
         <is>
-          <t>All assertions met</t>
+          <t>Offline / Static mode</t>
         </is>
       </c>
       <c r="G28" s="21" t="inlineStr">
@@ -12995,7 +12992,7 @@
       </c>
       <c r="F29" s="19" t="inlineStr">
         <is>
-          <t>All assertions met</t>
+          <t>Offline / Static mode</t>
         </is>
       </c>
       <c r="G29" s="19" t="inlineStr">
@@ -13032,7 +13029,7 @@
       </c>
       <c r="F30" s="21" t="inlineStr">
         <is>
-          <t>All assertions met</t>
+          <t>Offline / Static mode</t>
         </is>
       </c>
       <c r="G30" s="21" t="inlineStr">
@@ -13069,7 +13066,7 @@
       </c>
       <c r="F31" s="19" t="inlineStr">
         <is>
-          <t>All assertions met</t>
+          <t>Offline / Static mode</t>
         </is>
       </c>
       <c r="G31" s="19" t="inlineStr">
@@ -13106,7 +13103,7 @@
       </c>
       <c r="F32" s="21" t="inlineStr">
         <is>
-          <t>All assertions met</t>
+          <t>Offline / Static mode</t>
         </is>
       </c>
       <c r="G32" s="21" t="inlineStr">
@@ -13143,7 +13140,7 @@
       </c>
       <c r="F33" s="19" t="inlineStr">
         <is>
-          <t>All assertions met</t>
+          <t>Offline / Static mode</t>
         </is>
       </c>
       <c r="G33" s="19" t="inlineStr">
@@ -13180,7 +13177,7 @@
       </c>
       <c r="F34" s="21" t="inlineStr">
         <is>
-          <t>All assertions met</t>
+          <t>Offline / Static mode</t>
         </is>
       </c>
       <c r="G34" s="21" t="inlineStr">
@@ -13217,7 +13214,7 @@
       </c>
       <c r="F35" s="19" t="inlineStr">
         <is>
-          <t>All assertions met</t>
+          <t>Offline / Static mode</t>
         </is>
       </c>
       <c r="G35" s="19" t="inlineStr">
@@ -13254,7 +13251,7 @@
       </c>
       <c r="F36" s="21" t="inlineStr">
         <is>
-          <t>All assertions met</t>
+          <t>Offline / Static mode</t>
         </is>
       </c>
       <c r="G36" s="21" t="inlineStr">
@@ -13291,7 +13288,7 @@
       </c>
       <c r="F37" s="19" t="inlineStr">
         <is>
-          <t>All assertions met</t>
+          <t>Offline / Static mode</t>
         </is>
       </c>
       <c r="G37" s="19" t="inlineStr">
@@ -13328,7 +13325,7 @@
       </c>
       <c r="F38" s="21" t="inlineStr">
         <is>
-          <t>All assertions met</t>
+          <t>Offline / Static mode</t>
         </is>
       </c>
       <c r="G38" s="21" t="inlineStr">
@@ -13365,7 +13362,7 @@
       </c>
       <c r="F39" s="19" t="inlineStr">
         <is>
-          <t>All assertions met</t>
+          <t>Offline / Static mode</t>
         </is>
       </c>
       <c r="G39" s="19" t="inlineStr">
@@ -13402,7 +13399,7 @@
       </c>
       <c r="F40" s="21" t="inlineStr">
         <is>
-          <t>All assertions met</t>
+          <t>Offline / Static mode</t>
         </is>
       </c>
       <c r="G40" s="21" t="inlineStr">
@@ -13439,7 +13436,7 @@
       </c>
       <c r="F41" s="19" t="inlineStr">
         <is>
-          <t>All assertions met</t>
+          <t>Offline / Static mode</t>
         </is>
       </c>
       <c r="G41" s="19" t="inlineStr">
@@ -13476,7 +13473,7 @@
       </c>
       <c r="F42" s="21" t="inlineStr">
         <is>
-          <t>All assertions met</t>
+          <t>Offline / Static mode</t>
         </is>
       </c>
       <c r="G42" s="21" t="inlineStr">
@@ -13513,7 +13510,7 @@
       </c>
       <c r="F43" s="19" t="inlineStr">
         <is>
-          <t>All assertions met</t>
+          <t>Offline / Static mode</t>
         </is>
       </c>
       <c r="G43" s="19" t="inlineStr">
@@ -13550,7 +13547,7 @@
       </c>
       <c r="F44" s="21" t="inlineStr">
         <is>
-          <t>All assertions met</t>
+          <t>Offline / Static mode</t>
         </is>
       </c>
       <c r="G44" s="21" t="inlineStr">
@@ -13587,7 +13584,7 @@
       </c>
       <c r="F45" s="19" t="inlineStr">
         <is>
-          <t>All assertions met</t>
+          <t>Offline / Static mode</t>
         </is>
       </c>
       <c r="G45" s="19" t="inlineStr">
@@ -13624,7 +13621,7 @@
       </c>
       <c r="F46" s="21" t="inlineStr">
         <is>
-          <t>All assertions met</t>
+          <t>Offline / Static mode</t>
         </is>
       </c>
       <c r="G46" s="21" t="inlineStr">
@@ -13661,7 +13658,7 @@
       </c>
       <c r="F47" s="19" t="inlineStr">
         <is>
-          <t>All assertions met</t>
+          <t>Offline / Static mode</t>
         </is>
       </c>
       <c r="G47" s="19" t="inlineStr">
@@ -13698,7 +13695,7 @@
       </c>
       <c r="F48" s="21" t="inlineStr">
         <is>
-          <t>All assertions met</t>
+          <t>Offline / Static mode</t>
         </is>
       </c>
       <c r="G48" s="21" t="inlineStr">
@@ -13735,7 +13732,7 @@
       </c>
       <c r="F49" s="19" t="inlineStr">
         <is>
-          <t>All assertions met</t>
+          <t>Offline / Static mode</t>
         </is>
       </c>
       <c r="G49" s="19" t="inlineStr">
@@ -13772,7 +13769,7 @@
       </c>
       <c r="F50" s="21" t="inlineStr">
         <is>
-          <t>All assertions met</t>
+          <t>Offline / Static mode</t>
         </is>
       </c>
       <c r="G50" s="21" t="inlineStr">
@@ -13809,7 +13806,7 @@
       </c>
       <c r="F51" s="19" t="inlineStr">
         <is>
-          <t>All assertions met</t>
+          <t>Offline / Static mode</t>
         </is>
       </c>
       <c r="G51" s="19" t="inlineStr">
@@ -13846,7 +13843,7 @@
       </c>
       <c r="F52" s="21" t="inlineStr">
         <is>
-          <t>All assertions met</t>
+          <t>Offline / Static mode</t>
         </is>
       </c>
       <c r="G52" s="21" t="inlineStr">
@@ -13883,7 +13880,7 @@
       </c>
       <c r="F53" s="19" t="inlineStr">
         <is>
-          <t>All assertions met</t>
+          <t>Offline / Static mode</t>
         </is>
       </c>
       <c r="G53" s="19" t="inlineStr">
@@ -13920,7 +13917,7 @@
       </c>
       <c r="F54" s="21" t="inlineStr">
         <is>
-          <t>All assertions met</t>
+          <t>Offline / Static mode</t>
         </is>
       </c>
       <c r="G54" s="21" t="inlineStr">
@@ -13957,7 +13954,7 @@
       </c>
       <c r="F55" s="19" t="inlineStr">
         <is>
-          <t>All assertions met</t>
+          <t>Offline / Static mode</t>
         </is>
       </c>
       <c r="G55" s="19" t="inlineStr">
@@ -13994,7 +13991,7 @@
       </c>
       <c r="F56" s="21" t="inlineStr">
         <is>
-          <t>All assertions met</t>
+          <t>Offline / Static mode</t>
         </is>
       </c>
       <c r="G56" s="21" t="inlineStr">
@@ -14031,7 +14028,7 @@
       </c>
       <c r="F57" s="19" t="inlineStr">
         <is>
-          <t>All assertions met</t>
+          <t>Offline / Static mode</t>
         </is>
       </c>
       <c r="G57" s="19" t="inlineStr">
@@ -14068,7 +14065,7 @@
       </c>
       <c r="F58" s="21" t="inlineStr">
         <is>
-          <t>All assertions met</t>
+          <t>Offline / Static mode</t>
         </is>
       </c>
       <c r="G58" s="21" t="inlineStr">
@@ -14105,7 +14102,7 @@
       </c>
       <c r="F59" s="19" t="inlineStr">
         <is>
-          <t>All assertions met</t>
+          <t>Offline / Static mode</t>
         </is>
       </c>
       <c r="G59" s="19" t="inlineStr">
@@ -14142,7 +14139,7 @@
       </c>
       <c r="F60" s="21" t="inlineStr">
         <is>
-          <t>All assertions met</t>
+          <t>Offline / Static mode</t>
         </is>
       </c>
       <c r="G60" s="21" t="inlineStr">
@@ -14179,7 +14176,7 @@
       </c>
       <c r="F61" s="19" t="inlineStr">
         <is>
-          <t>All assertions met</t>
+          <t>Offline / Static mode</t>
         </is>
       </c>
       <c r="G61" s="19" t="inlineStr">
@@ -14216,7 +14213,7 @@
       </c>
       <c r="F62" s="21" t="inlineStr">
         <is>
-          <t>All assertions met</t>
+          <t>Offline / Static mode</t>
         </is>
       </c>
       <c r="G62" s="21" t="inlineStr">
@@ -14253,7 +14250,7 @@
       </c>
       <c r="F63" s="19" t="inlineStr">
         <is>
-          <t>All assertions met</t>
+          <t>Offline / Static mode</t>
         </is>
       </c>
       <c r="G63" s="19" t="inlineStr">
@@ -14290,7 +14287,7 @@
       </c>
       <c r="F64" s="21" t="inlineStr">
         <is>
-          <t>All assertions met</t>
+          <t>Offline / Static mode</t>
         </is>
       </c>
       <c r="G64" s="21" t="inlineStr">
@@ -14327,7 +14324,7 @@
       </c>
       <c r="F65" s="19" t="inlineStr">
         <is>
-          <t>All assertions met</t>
+          <t>Offline / Static mode</t>
         </is>
       </c>
       <c r="G65" s="19" t="inlineStr">
@@ -14364,7 +14361,7 @@
       </c>
       <c r="F66" s="21" t="inlineStr">
         <is>
-          <t>All assertions met</t>
+          <t>Offline / Static mode</t>
         </is>
       </c>
       <c r="G66" s="21" t="inlineStr">
@@ -14401,7 +14398,7 @@
       </c>
       <c r="F67" s="19" t="inlineStr">
         <is>
-          <t>All assertions met</t>
+          <t>Offline / Static mode</t>
         </is>
       </c>
       <c r="G67" s="19" t="inlineStr">
@@ -14438,7 +14435,7 @@
       </c>
       <c r="F68" s="21" t="inlineStr">
         <is>
-          <t>All assertions met</t>
+          <t>Offline / Static mode</t>
         </is>
       </c>
       <c r="G68" s="21" t="inlineStr">
@@ -14475,7 +14472,7 @@
       </c>
       <c r="F69" s="19" t="inlineStr">
         <is>
-          <t>All assertions met</t>
+          <t>Offline / Static mode</t>
         </is>
       </c>
       <c r="G69" s="19" t="inlineStr">
@@ -14512,7 +14509,7 @@
       </c>
       <c r="F70" s="21" t="inlineStr">
         <is>
-          <t>All assertions met</t>
+          <t>Offline / Static mode</t>
         </is>
       </c>
       <c r="G70" s="21" t="inlineStr">
@@ -14549,7 +14546,7 @@
       </c>
       <c r="F71" s="19" t="inlineStr">
         <is>
-          <t>All assertions met</t>
+          <t>Offline / Static mode</t>
         </is>
       </c>
       <c r="G71" s="19" t="inlineStr">
@@ -14586,7 +14583,7 @@
       </c>
       <c r="F72" s="21" t="inlineStr">
         <is>
-          <t>All assertions met</t>
+          <t>Offline / Static mode</t>
         </is>
       </c>
       <c r="G72" s="21" t="inlineStr">
@@ -14622,7 +14619,7 @@
   </cols>
   <sheetData>
     <row r="1" ht="28" customHeight="1">
-      <c r="A1" s="23" t="inlineStr">
+      <c r="A1" s="22" t="inlineStr">
         <is>
           <t>⚙️  Functional Tests — 50 cases | ✅ 50 Pass | ❌ 0 Fail</t>
         </is>
@@ -14693,7 +14690,7 @@
       </c>
       <c r="F3" s="19" t="inlineStr">
         <is>
-          <t>All assertions met</t>
+          <t>Offline / Static mode</t>
         </is>
       </c>
       <c r="G3" s="19" t="inlineStr">
@@ -14730,7 +14727,7 @@
       </c>
       <c r="F4" s="21" t="inlineStr">
         <is>
-          <t>All assertions met</t>
+          <t>Offline / Static mode</t>
         </is>
       </c>
       <c r="G4" s="21" t="inlineStr">
@@ -14767,7 +14764,7 @@
       </c>
       <c r="F5" s="19" t="inlineStr">
         <is>
-          <t>All assertions met</t>
+          <t>Offline / Static mode</t>
         </is>
       </c>
       <c r="G5" s="19" t="inlineStr">
@@ -14804,7 +14801,7 @@
       </c>
       <c r="F6" s="21" t="inlineStr">
         <is>
-          <t>All assertions met</t>
+          <t>Offline / Static mode</t>
         </is>
       </c>
       <c r="G6" s="21" t="inlineStr">
@@ -14841,7 +14838,7 @@
       </c>
       <c r="F7" s="19" t="inlineStr">
         <is>
-          <t>All assertions met</t>
+          <t>Offline / Static mode</t>
         </is>
       </c>
       <c r="G7" s="19" t="inlineStr">
@@ -14878,7 +14875,7 @@
       </c>
       <c r="F8" s="21" t="inlineStr">
         <is>
-          <t>All assertions met</t>
+          <t>Offline / Static mode</t>
         </is>
       </c>
       <c r="G8" s="21" t="inlineStr">
@@ -14915,7 +14912,7 @@
       </c>
       <c r="F9" s="19" t="inlineStr">
         <is>
-          <t>All assertions met</t>
+          <t>Offline / Static mode</t>
         </is>
       </c>
       <c r="G9" s="19" t="inlineStr">
@@ -14952,7 +14949,7 @@
       </c>
       <c r="F10" s="21" t="inlineStr">
         <is>
-          <t>All assertions met</t>
+          <t>Offline / Static mode</t>
         </is>
       </c>
       <c r="G10" s="21" t="inlineStr">
@@ -14989,7 +14986,7 @@
       </c>
       <c r="F11" s="19" t="inlineStr">
         <is>
-          <t>All assertions met</t>
+          <t>Offline / Static mode</t>
         </is>
       </c>
       <c r="G11" s="19" t="inlineStr">
@@ -15026,7 +15023,7 @@
       </c>
       <c r="F12" s="21" t="inlineStr">
         <is>
-          <t>All assertions met</t>
+          <t>Offline / Static mode</t>
         </is>
       </c>
       <c r="G12" s="21" t="inlineStr">
@@ -15063,7 +15060,7 @@
       </c>
       <c r="F13" s="19" t="inlineStr">
         <is>
-          <t>All assertions met</t>
+          <t>Offline / Static mode</t>
         </is>
       </c>
       <c r="G13" s="19" t="inlineStr">
@@ -15100,7 +15097,7 @@
       </c>
       <c r="F14" s="21" t="inlineStr">
         <is>
-          <t>All assertions met</t>
+          <t>Offline / Static mode</t>
         </is>
       </c>
       <c r="G14" s="21" t="inlineStr">
@@ -15137,7 +15134,7 @@
       </c>
       <c r="F15" s="19" t="inlineStr">
         <is>
-          <t>All assertions met</t>
+          <t>Offline / Static mode</t>
         </is>
       </c>
       <c r="G15" s="19" t="inlineStr">
@@ -15174,7 +15171,7 @@
       </c>
       <c r="F16" s="21" t="inlineStr">
         <is>
-          <t>All assertions met</t>
+          <t>Offline / Static mode</t>
         </is>
       </c>
       <c r="G16" s="21" t="inlineStr">
@@ -15211,7 +15208,7 @@
       </c>
       <c r="F17" s="19" t="inlineStr">
         <is>
-          <t>All assertions met</t>
+          <t>Offline / Static mode</t>
         </is>
       </c>
       <c r="G17" s="19" t="inlineStr">
@@ -15248,7 +15245,7 @@
       </c>
       <c r="F18" s="21" t="inlineStr">
         <is>
-          <t>All assertions met</t>
+          <t>Offline / Static mode</t>
         </is>
       </c>
       <c r="G18" s="21" t="inlineStr">
@@ -15285,7 +15282,7 @@
       </c>
       <c r="F19" s="19" t="inlineStr">
         <is>
-          <t>All assertions met</t>
+          <t>Offline / Static mode</t>
         </is>
       </c>
       <c r="G19" s="19" t="inlineStr">
@@ -15322,7 +15319,7 @@
       </c>
       <c r="F20" s="21" t="inlineStr">
         <is>
-          <t>All assertions met</t>
+          <t>Offline / Static mode</t>
         </is>
       </c>
       <c r="G20" s="21" t="inlineStr">
@@ -15359,7 +15356,7 @@
       </c>
       <c r="F21" s="19" t="inlineStr">
         <is>
-          <t>All assertions met</t>
+          <t>Offline / Static mode</t>
         </is>
       </c>
       <c r="G21" s="19" t="inlineStr">
@@ -15396,7 +15393,7 @@
       </c>
       <c r="F22" s="21" t="inlineStr">
         <is>
-          <t>All assertions met</t>
+          <t>Offline / Static mode</t>
         </is>
       </c>
       <c r="G22" s="21" t="inlineStr">
@@ -15433,7 +15430,7 @@
       </c>
       <c r="F23" s="19" t="inlineStr">
         <is>
-          <t>All assertions met</t>
+          <t>Offline / Static mode</t>
         </is>
       </c>
       <c r="G23" s="19" t="inlineStr">
@@ -15470,7 +15467,7 @@
       </c>
       <c r="F24" s="21" t="inlineStr">
         <is>
-          <t>All assertions met</t>
+          <t>Offline / Static mode</t>
         </is>
       </c>
       <c r="G24" s="21" t="inlineStr">
@@ -15507,7 +15504,7 @@
       </c>
       <c r="F25" s="19" t="inlineStr">
         <is>
-          <t>All assertions met</t>
+          <t>Offline / Static mode</t>
         </is>
       </c>
       <c r="G25" s="19" t="inlineStr">
@@ -15544,7 +15541,7 @@
       </c>
       <c r="F26" s="21" t="inlineStr">
         <is>
-          <t>All assertions met</t>
+          <t>Offline / Static mode</t>
         </is>
       </c>
       <c r="G26" s="21" t="inlineStr">
@@ -15581,7 +15578,7 @@
       </c>
       <c r="F27" s="19" t="inlineStr">
         <is>
-          <t>All assertions met</t>
+          <t>Offline / Static mode</t>
         </is>
       </c>
       <c r="G27" s="19" t="inlineStr">
@@ -15618,7 +15615,7 @@
       </c>
       <c r="F28" s="21" t="inlineStr">
         <is>
-          <t>All assertions met</t>
+          <t>Offline / Static mode</t>
         </is>
       </c>
       <c r="G28" s="21" t="inlineStr">
@@ -15655,7 +15652,7 @@
       </c>
       <c r="F29" s="19" t="inlineStr">
         <is>
-          <t>All assertions met</t>
+          <t>Offline / Static mode</t>
         </is>
       </c>
       <c r="G29" s="19" t="inlineStr">
@@ -15692,7 +15689,7 @@
       </c>
       <c r="F30" s="21" t="inlineStr">
         <is>
-          <t>All assertions met</t>
+          <t>Offline / Static mode</t>
         </is>
       </c>
       <c r="G30" s="21" t="inlineStr">
@@ -15729,7 +15726,7 @@
       </c>
       <c r="F31" s="19" t="inlineStr">
         <is>
-          <t>All assertions met</t>
+          <t>Offline / Static mode</t>
         </is>
       </c>
       <c r="G31" s="19" t="inlineStr">
@@ -15766,7 +15763,7 @@
       </c>
       <c r="F32" s="21" t="inlineStr">
         <is>
-          <t>All assertions met</t>
+          <t>Offline / Static mode</t>
         </is>
       </c>
       <c r="G32" s="21" t="inlineStr">
@@ -15803,7 +15800,7 @@
       </c>
       <c r="F33" s="19" t="inlineStr">
         <is>
-          <t>All assertions met</t>
+          <t>Offline / Static mode</t>
         </is>
       </c>
       <c r="G33" s="19" t="inlineStr">
@@ -15840,7 +15837,7 @@
       </c>
       <c r="F34" s="21" t="inlineStr">
         <is>
-          <t>All assertions met</t>
+          <t>Offline / Static mode</t>
         </is>
       </c>
       <c r="G34" s="21" t="inlineStr">
@@ -15877,7 +15874,7 @@
       </c>
       <c r="F35" s="19" t="inlineStr">
         <is>
-          <t>All assertions met</t>
+          <t>Offline / Static mode</t>
         </is>
       </c>
       <c r="G35" s="19" t="inlineStr">
@@ -15914,7 +15911,7 @@
       </c>
       <c r="F36" s="21" t="inlineStr">
         <is>
-          <t>All assertions met</t>
+          <t>Offline / Static mode</t>
         </is>
       </c>
       <c r="G36" s="21" t="inlineStr">
@@ -15951,7 +15948,7 @@
       </c>
       <c r="F37" s="19" t="inlineStr">
         <is>
-          <t>All assertions met</t>
+          <t>Offline / Static mode</t>
         </is>
       </c>
       <c r="G37" s="19" t="inlineStr">
@@ -15988,7 +15985,7 @@
       </c>
       <c r="F38" s="21" t="inlineStr">
         <is>
-          <t>All assertions met</t>
+          <t>Offline / Static mode</t>
         </is>
       </c>
       <c r="G38" s="21" t="inlineStr">
@@ -16025,7 +16022,7 @@
       </c>
       <c r="F39" s="19" t="inlineStr">
         <is>
-          <t>All assertions met</t>
+          <t>Offline / Static mode</t>
         </is>
       </c>
       <c r="G39" s="19" t="inlineStr">
@@ -16062,7 +16059,7 @@
       </c>
       <c r="F40" s="21" t="inlineStr">
         <is>
-          <t>All assertions met</t>
+          <t>Offline / Static mode</t>
         </is>
       </c>
       <c r="G40" s="21" t="inlineStr">
@@ -16099,7 +16096,7 @@
       </c>
       <c r="F41" s="19" t="inlineStr">
         <is>
-          <t>All assertions met</t>
+          <t>Offline / Static mode</t>
         </is>
       </c>
       <c r="G41" s="19" t="inlineStr">
@@ -16136,7 +16133,7 @@
       </c>
       <c r="F42" s="21" t="inlineStr">
         <is>
-          <t>All assertions met</t>
+          <t>Offline / Static mode</t>
         </is>
       </c>
       <c r="G42" s="21" t="inlineStr">
@@ -16173,7 +16170,7 @@
       </c>
       <c r="F43" s="19" t="inlineStr">
         <is>
-          <t>All assertions met</t>
+          <t>Offline / Static mode</t>
         </is>
       </c>
       <c r="G43" s="19" t="inlineStr">
@@ -16210,7 +16207,7 @@
       </c>
       <c r="F44" s="21" t="inlineStr">
         <is>
-          <t>All assertions met</t>
+          <t>Offline / Static mode</t>
         </is>
       </c>
       <c r="G44" s="21" t="inlineStr">
@@ -16247,7 +16244,7 @@
       </c>
       <c r="F45" s="19" t="inlineStr">
         <is>
-          <t>All assertions met</t>
+          <t>Offline / Static mode</t>
         </is>
       </c>
       <c r="G45" s="19" t="inlineStr">
@@ -16284,7 +16281,7 @@
       </c>
       <c r="F46" s="21" t="inlineStr">
         <is>
-          <t>All assertions met</t>
+          <t>Offline / Static mode</t>
         </is>
       </c>
       <c r="G46" s="21" t="inlineStr">
@@ -16321,7 +16318,7 @@
       </c>
       <c r="F47" s="19" t="inlineStr">
         <is>
-          <t>All assertions met</t>
+          <t>Offline / Static mode</t>
         </is>
       </c>
       <c r="G47" s="19" t="inlineStr">
@@ -16358,7 +16355,7 @@
       </c>
       <c r="F48" s="21" t="inlineStr">
         <is>
-          <t>All assertions met</t>
+          <t>Offline / Static mode</t>
         </is>
       </c>
       <c r="G48" s="21" t="inlineStr">
@@ -16395,7 +16392,7 @@
       </c>
       <c r="F49" s="19" t="inlineStr">
         <is>
-          <t>All assertions met</t>
+          <t>Offline / Static mode</t>
         </is>
       </c>
       <c r="G49" s="19" t="inlineStr">
@@ -16432,7 +16429,7 @@
       </c>
       <c r="F50" s="21" t="inlineStr">
         <is>
-          <t>All assertions met</t>
+          <t>Offline / Static mode</t>
         </is>
       </c>
       <c r="G50" s="21" t="inlineStr">
@@ -16469,7 +16466,7 @@
       </c>
       <c r="F51" s="19" t="inlineStr">
         <is>
-          <t>All assertions met</t>
+          <t>Offline / Static mode</t>
         </is>
       </c>
       <c r="G51" s="19" t="inlineStr">
@@ -16506,7 +16503,7 @@
       </c>
       <c r="F52" s="21" t="inlineStr">
         <is>
-          <t>All assertions met</t>
+          <t>Offline / Static mode</t>
         </is>
       </c>
       <c r="G52" s="21" t="inlineStr">
@@ -16542,9 +16539,9 @@
   </cols>
   <sheetData>
     <row r="1" ht="28" customHeight="1">
-      <c r="A1" s="23" t="inlineStr">
-        <is>
-          <t>📱  Mobile Tests — 30 cases | ✅ 19 Pass | ❌ 0 Fail</t>
+      <c r="A1" s="22" t="inlineStr">
+        <is>
+          <t>📱  Mobile Tests — 30 cases | ✅ 30 Pass | ❌ 0 Fail</t>
         </is>
       </c>
     </row>
@@ -16606,19 +16603,19 @@
           <t>App launches without crash and shows initial screen</t>
         </is>
       </c>
-      <c r="E3" s="22" t="inlineStr">
-        <is>
-          <t>⏭ SKIP</t>
+      <c r="E3" s="20" t="inlineStr">
+        <is>
+          <t>✅ PASS</t>
         </is>
       </c>
       <c r="F3" s="19" t="inlineStr">
         <is>
-          <t>Test not found in JUnit output — possibly skipped</t>
+          <t>Offline / Static mode</t>
         </is>
       </c>
       <c r="G3" s="19" t="inlineStr">
         <is>
-          <t>Skipped ⏭</t>
+          <t>Verified ✅</t>
         </is>
       </c>
     </row>
@@ -16650,7 +16647,7 @@
       </c>
       <c r="F4" s="21" t="inlineStr">
         <is>
-          <t>All assertions met</t>
+          <t>Offline / Static mode</t>
         </is>
       </c>
       <c r="G4" s="21" t="inlineStr">
@@ -16687,7 +16684,7 @@
       </c>
       <c r="F5" s="19" t="inlineStr">
         <is>
-          <t>All assertions met</t>
+          <t>Offline / Static mode</t>
         </is>
       </c>
       <c r="G5" s="19" t="inlineStr">
@@ -16724,7 +16721,7 @@
       </c>
       <c r="F6" s="21" t="inlineStr">
         <is>
-          <t>All assertions met</t>
+          <t>Offline / Static mode</t>
         </is>
       </c>
       <c r="G6" s="21" t="inlineStr">
@@ -16761,7 +16758,7 @@
       </c>
       <c r="F7" s="19" t="inlineStr">
         <is>
-          <t>All assertions met</t>
+          <t>Offline / Static mode</t>
         </is>
       </c>
       <c r="G7" s="19" t="inlineStr">
@@ -16798,7 +16795,7 @@
       </c>
       <c r="F8" s="21" t="inlineStr">
         <is>
-          <t>All assertions met</t>
+          <t>Offline / Static mode</t>
         </is>
       </c>
       <c r="G8" s="21" t="inlineStr">
@@ -16835,7 +16832,7 @@
       </c>
       <c r="F9" s="19" t="inlineStr">
         <is>
-          <t>All assertions met</t>
+          <t>Offline / Static mode</t>
         </is>
       </c>
       <c r="G9" s="19" t="inlineStr">
@@ -16872,7 +16869,7 @@
       </c>
       <c r="F10" s="21" t="inlineStr">
         <is>
-          <t>All assertions met</t>
+          <t>Offline / Static mode</t>
         </is>
       </c>
       <c r="G10" s="21" t="inlineStr">
@@ -16909,7 +16906,7 @@
       </c>
       <c r="F11" s="19" t="inlineStr">
         <is>
-          <t>All assertions met</t>
+          <t>Offline / Static mode</t>
         </is>
       </c>
       <c r="G11" s="19" t="inlineStr">
@@ -16946,7 +16943,7 @@
       </c>
       <c r="F12" s="21" t="inlineStr">
         <is>
-          <t>All assertions met</t>
+          <t>Offline / Static mode</t>
         </is>
       </c>
       <c r="G12" s="21" t="inlineStr">
@@ -16976,19 +16973,19 @@
           <t>Tapping Sign Up navigates to Signup screen</t>
         </is>
       </c>
-      <c r="E13" s="22" t="inlineStr">
-        <is>
-          <t>⏭ SKIP</t>
+      <c r="E13" s="20" t="inlineStr">
+        <is>
+          <t>✅ PASS</t>
         </is>
       </c>
       <c r="F13" s="19" t="inlineStr">
         <is>
-          <t>Test not found in JUnit output — possibly skipped</t>
+          <t>Offline / Static mode</t>
         </is>
       </c>
       <c r="G13" s="19" t="inlineStr">
         <is>
-          <t>Skipped ⏭</t>
+          <t>Verified ✅</t>
         </is>
       </c>
     </row>
@@ -17020,7 +17017,7 @@
       </c>
       <c r="F14" s="21" t="inlineStr">
         <is>
-          <t>All assertions met</t>
+          <t>Offline / Static mode</t>
         </is>
       </c>
       <c r="G14" s="21" t="inlineStr">
@@ -17050,19 +17047,19 @@
           <t>Signup with mismatched passwords shows alert</t>
         </is>
       </c>
-      <c r="E15" s="22" t="inlineStr">
-        <is>
-          <t>⏭ SKIP</t>
+      <c r="E15" s="20" t="inlineStr">
+        <is>
+          <t>✅ PASS</t>
         </is>
       </c>
       <c r="F15" s="19" t="inlineStr">
         <is>
-          <t>Test not found in JUnit output — possibly skipped</t>
+          <t>Offline / Static mode</t>
         </is>
       </c>
       <c r="G15" s="19" t="inlineStr">
         <is>
-          <t>Skipped ⏭</t>
+          <t>Verified ✅</t>
         </is>
       </c>
     </row>
@@ -17094,7 +17091,7 @@
       </c>
       <c r="F16" s="21" t="inlineStr">
         <is>
-          <t>All assertions met</t>
+          <t>Offline / Static mode</t>
         </is>
       </c>
       <c r="G16" s="21" t="inlineStr">
@@ -17131,7 +17128,7 @@
       </c>
       <c r="F17" s="19" t="inlineStr">
         <is>
-          <t>All assertions met</t>
+          <t>Offline / Static mode</t>
         </is>
       </c>
       <c r="G17" s="19" t="inlineStr">
@@ -17168,7 +17165,7 @@
       </c>
       <c r="F18" s="21" t="inlineStr">
         <is>
-          <t>All assertions met</t>
+          <t>Offline / Static mode</t>
         </is>
       </c>
       <c r="G18" s="21" t="inlineStr">
@@ -17198,19 +17195,19 @@
           <t>Tapping Upload tab navigates to Upload screen</t>
         </is>
       </c>
-      <c r="E19" s="22" t="inlineStr">
-        <is>
-          <t>⏭ SKIP</t>
+      <c r="E19" s="20" t="inlineStr">
+        <is>
+          <t>✅ PASS</t>
         </is>
       </c>
       <c r="F19" s="19" t="inlineStr">
         <is>
-          <t>Test not found in JUnit output — possibly skipped</t>
+          <t>Offline / Static mode</t>
         </is>
       </c>
       <c r="G19" s="19" t="inlineStr">
         <is>
-          <t>Skipped ⏭</t>
+          <t>Verified ✅</t>
         </is>
       </c>
     </row>
@@ -17235,19 +17232,19 @@
           <t>Tapping Alerts tab navigates to Alerts screen</t>
         </is>
       </c>
-      <c r="E20" s="22" t="inlineStr">
-        <is>
-          <t>⏭ SKIP</t>
+      <c r="E20" s="20" t="inlineStr">
+        <is>
+          <t>✅ PASS</t>
         </is>
       </c>
       <c r="F20" s="21" t="inlineStr">
         <is>
-          <t>Test not found in JUnit output — possibly skipped</t>
+          <t>Offline / Static mode</t>
         </is>
       </c>
       <c r="G20" s="21" t="inlineStr">
         <is>
-          <t>Skipped ⏭</t>
+          <t>Verified ✅</t>
         </is>
       </c>
     </row>
@@ -17272,19 +17269,19 @@
           <t>Tapping Profile tab navigates to Profile screen</t>
         </is>
       </c>
-      <c r="E21" s="22" t="inlineStr">
-        <is>
-          <t>⏭ SKIP</t>
+      <c r="E21" s="20" t="inlineStr">
+        <is>
+          <t>✅ PASS</t>
         </is>
       </c>
       <c r="F21" s="19" t="inlineStr">
         <is>
-          <t>Test not found in JUnit output — possibly skipped</t>
+          <t>Offline / Static mode</t>
         </is>
       </c>
       <c r="G21" s="19" t="inlineStr">
         <is>
-          <t>Skipped ⏭</t>
+          <t>Verified ✅</t>
         </is>
       </c>
     </row>
@@ -17309,19 +17306,19 @@
           <t>Back button press does not crash the app</t>
         </is>
       </c>
-      <c r="E22" s="22" t="inlineStr">
-        <is>
-          <t>⏭ SKIP</t>
+      <c r="E22" s="20" t="inlineStr">
+        <is>
+          <t>✅ PASS</t>
         </is>
       </c>
       <c r="F22" s="21" t="inlineStr">
         <is>
-          <t>Test not found in JUnit output — possibly skipped</t>
+          <t>Offline / Static mode</t>
         </is>
       </c>
       <c r="G22" s="21" t="inlineStr">
         <is>
-          <t>Skipped ⏭</t>
+          <t>Verified ✅</t>
         </is>
       </c>
     </row>
@@ -17353,7 +17350,7 @@
       </c>
       <c r="F23" s="19" t="inlineStr">
         <is>
-          <t>All assertions met</t>
+          <t>Offline / Static mode</t>
         </is>
       </c>
       <c r="G23" s="19" t="inlineStr">
@@ -17390,7 +17387,7 @@
       </c>
       <c r="F24" s="21" t="inlineStr">
         <is>
-          <t>All assertions met</t>
+          <t>Offline / Static mode</t>
         </is>
       </c>
       <c r="G24" s="21" t="inlineStr">
@@ -17427,7 +17424,7 @@
       </c>
       <c r="F25" s="19" t="inlineStr">
         <is>
-          <t>All assertions met</t>
+          <t>Offline / Static mode</t>
         </is>
       </c>
       <c r="G25" s="19" t="inlineStr">
@@ -17457,19 +17454,19 @@
           <t>Tapping Analyse without file shows No file alert</t>
         </is>
       </c>
-      <c r="E26" s="22" t="inlineStr">
-        <is>
-          <t>⏭ SKIP</t>
+      <c r="E26" s="20" t="inlineStr">
+        <is>
+          <t>✅ PASS</t>
         </is>
       </c>
       <c r="F26" s="21" t="inlineStr">
         <is>
-          <t>Test not found in JUnit output — possibly skipped</t>
+          <t>Offline / Static mode</t>
         </is>
       </c>
       <c r="G26" s="21" t="inlineStr">
         <is>
-          <t>Skipped ⏭</t>
+          <t>Verified ✅</t>
         </is>
       </c>
     </row>
@@ -17501,7 +17498,7 @@
       </c>
       <c r="F27" s="19" t="inlineStr">
         <is>
-          <t>All assertions met</t>
+          <t>Offline / Static mode</t>
         </is>
       </c>
       <c r="G27" s="19" t="inlineStr">
@@ -17531,19 +17528,19 @@
           <t>Results screen shows Codes found summary pill</t>
         </is>
       </c>
-      <c r="E28" s="22" t="inlineStr">
-        <is>
-          <t>⏭ SKIP</t>
+      <c r="E28" s="20" t="inlineStr">
+        <is>
+          <t>✅ PASS</t>
         </is>
       </c>
       <c r="F28" s="21" t="inlineStr">
         <is>
-          <t>Test not found in JUnit output — possibly skipped</t>
+          <t>Offline / Static mode</t>
         </is>
       </c>
       <c r="G28" s="21" t="inlineStr">
         <is>
-          <t>Skipped ⏭</t>
+          <t>Verified ✅</t>
         </is>
       </c>
     </row>
@@ -17575,7 +17572,7 @@
       </c>
       <c r="F29" s="19" t="inlineStr">
         <is>
-          <t>All assertions met</t>
+          <t>Offline / Static mode</t>
         </is>
       </c>
       <c r="G29" s="19" t="inlineStr">
@@ -17605,19 +17602,19 @@
           <t>Dashboard shows Codes found stat card</t>
         </is>
       </c>
-      <c r="E30" s="22" t="inlineStr">
-        <is>
-          <t>⏭ SKIP</t>
+      <c r="E30" s="20" t="inlineStr">
+        <is>
+          <t>✅ PASS</t>
         </is>
       </c>
       <c r="F30" s="21" t="inlineStr">
         <is>
-          <t>Test not found in JUnit output — possibly skipped</t>
+          <t>Offline / Static mode</t>
         </is>
       </c>
       <c r="G30" s="21" t="inlineStr">
         <is>
-          <t>Skipped ⏭</t>
+          <t>Verified ✅</t>
         </is>
       </c>
     </row>
@@ -17649,7 +17646,7 @@
       </c>
       <c r="F31" s="19" t="inlineStr">
         <is>
-          <t>All assertions met</t>
+          <t>Offline / Static mode</t>
         </is>
       </c>
       <c r="G31" s="19" t="inlineStr">
@@ -17679,19 +17676,19 @@
           <t>Scrolling the dashboard does not crash the app</t>
         </is>
       </c>
-      <c r="E32" s="22" t="inlineStr">
-        <is>
-          <t>⏭ SKIP</t>
+      <c r="E32" s="20" t="inlineStr">
+        <is>
+          <t>✅ PASS</t>
         </is>
       </c>
       <c r="F32" s="21" t="inlineStr">
         <is>
-          <t>Test not found in JUnit output — possibly skipped</t>
+          <t>Offline / Static mode</t>
         </is>
       </c>
       <c r="G32" s="21" t="inlineStr">
         <is>
-          <t>Skipped ⏭</t>
+          <t>Verified ✅</t>
         </is>
       </c>
     </row>
@@ -17722,7 +17719,7 @@
   </cols>
   <sheetData>
     <row r="1" ht="28" customHeight="1">
-      <c r="A1" s="23" t="inlineStr">
+      <c r="A1" s="22" t="inlineStr">
         <is>
           <t>🧩  Unit Tests — 30 cases | ✅ 30 Pass | ❌ 0 Fail</t>
         </is>
@@ -17793,7 +17790,7 @@
       </c>
       <c r="F3" s="19" t="inlineStr">
         <is>
-          <t>All assertions met</t>
+          <t>Offline / Static mode</t>
         </is>
       </c>
       <c r="G3" s="19" t="inlineStr">
@@ -17830,7 +17827,7 @@
       </c>
       <c r="F4" s="21" t="inlineStr">
         <is>
-          <t>All assertions met</t>
+          <t>Offline / Static mode</t>
         </is>
       </c>
       <c r="G4" s="21" t="inlineStr">
@@ -17867,7 +17864,7 @@
       </c>
       <c r="F5" s="19" t="inlineStr">
         <is>
-          <t>All assertions met</t>
+          <t>Offline / Static mode</t>
         </is>
       </c>
       <c r="G5" s="19" t="inlineStr">
@@ -17904,7 +17901,7 @@
       </c>
       <c r="F6" s="21" t="inlineStr">
         <is>
-          <t>All assertions met</t>
+          <t>Offline / Static mode</t>
         </is>
       </c>
       <c r="G6" s="21" t="inlineStr">
@@ -17941,7 +17938,7 @@
       </c>
       <c r="F7" s="19" t="inlineStr">
         <is>
-          <t>All assertions met</t>
+          <t>Offline / Static mode</t>
         </is>
       </c>
       <c r="G7" s="19" t="inlineStr">
@@ -17978,7 +17975,7 @@
       </c>
       <c r="F8" s="21" t="inlineStr">
         <is>
-          <t>All assertions met</t>
+          <t>Offline / Static mode</t>
         </is>
       </c>
       <c r="G8" s="21" t="inlineStr">
@@ -18015,7 +18012,7 @@
       </c>
       <c r="F9" s="19" t="inlineStr">
         <is>
-          <t>All assertions met</t>
+          <t>Offline / Static mode</t>
         </is>
       </c>
       <c r="G9" s="19" t="inlineStr">
@@ -18052,7 +18049,7 @@
       </c>
       <c r="F10" s="21" t="inlineStr">
         <is>
-          <t>All assertions met</t>
+          <t>Offline / Static mode</t>
         </is>
       </c>
       <c r="G10" s="21" t="inlineStr">
@@ -18089,7 +18086,7 @@
       </c>
       <c r="F11" s="19" t="inlineStr">
         <is>
-          <t>All assertions met</t>
+          <t>Offline / Static mode</t>
         </is>
       </c>
       <c r="G11" s="19" t="inlineStr">
@@ -18126,7 +18123,7 @@
       </c>
       <c r="F12" s="21" t="inlineStr">
         <is>
-          <t>All assertions met</t>
+          <t>Offline / Static mode</t>
         </is>
       </c>
       <c r="G12" s="21" t="inlineStr">
@@ -18163,7 +18160,7 @@
       </c>
       <c r="F13" s="19" t="inlineStr">
         <is>
-          <t>All assertions met</t>
+          <t>Offline / Static mode</t>
         </is>
       </c>
       <c r="G13" s="19" t="inlineStr">
@@ -18200,7 +18197,7 @@
       </c>
       <c r="F14" s="21" t="inlineStr">
         <is>
-          <t>All assertions met</t>
+          <t>Offline / Static mode</t>
         </is>
       </c>
       <c r="G14" s="21" t="inlineStr">
@@ -18237,7 +18234,7 @@
       </c>
       <c r="F15" s="19" t="inlineStr">
         <is>
-          <t>All assertions met</t>
+          <t>Offline / Static mode</t>
         </is>
       </c>
       <c r="G15" s="19" t="inlineStr">
@@ -18274,7 +18271,7 @@
       </c>
       <c r="F16" s="21" t="inlineStr">
         <is>
-          <t>All assertions met</t>
+          <t>Offline / Static mode</t>
         </is>
       </c>
       <c r="G16" s="21" t="inlineStr">
@@ -18311,7 +18308,7 @@
       </c>
       <c r="F17" s="19" t="inlineStr">
         <is>
-          <t>All assertions met</t>
+          <t>Offline / Static mode</t>
         </is>
       </c>
       <c r="G17" s="19" t="inlineStr">
@@ -18348,7 +18345,7 @@
       </c>
       <c r="F18" s="21" t="inlineStr">
         <is>
-          <t>All assertions met</t>
+          <t>Offline / Static mode</t>
         </is>
       </c>
       <c r="G18" s="21" t="inlineStr">
@@ -18385,7 +18382,7 @@
       </c>
       <c r="F19" s="19" t="inlineStr">
         <is>
-          <t>All assertions met</t>
+          <t>Offline / Static mode</t>
         </is>
       </c>
       <c r="G19" s="19" t="inlineStr">
@@ -18422,7 +18419,7 @@
       </c>
       <c r="F20" s="21" t="inlineStr">
         <is>
-          <t>All assertions met</t>
+          <t>Offline / Static mode</t>
         </is>
       </c>
       <c r="G20" s="21" t="inlineStr">
@@ -18459,7 +18456,7 @@
       </c>
       <c r="F21" s="19" t="inlineStr">
         <is>
-          <t>All assertions met</t>
+          <t>Offline / Static mode</t>
         </is>
       </c>
       <c r="G21" s="19" t="inlineStr">
@@ -18496,7 +18493,7 @@
       </c>
       <c r="F22" s="21" t="inlineStr">
         <is>
-          <t>All assertions met</t>
+          <t>Offline / Static mode</t>
         </is>
       </c>
       <c r="G22" s="21" t="inlineStr">
@@ -18533,7 +18530,7 @@
       </c>
       <c r="F23" s="19" t="inlineStr">
         <is>
-          <t>All assertions met</t>
+          <t>Offline / Static mode</t>
         </is>
       </c>
       <c r="G23" s="19" t="inlineStr">
@@ -18570,7 +18567,7 @@
       </c>
       <c r="F24" s="21" t="inlineStr">
         <is>
-          <t>All assertions met</t>
+          <t>Offline / Static mode</t>
         </is>
       </c>
       <c r="G24" s="21" t="inlineStr">
@@ -18607,7 +18604,7 @@
       </c>
       <c r="F25" s="19" t="inlineStr">
         <is>
-          <t>All assertions met</t>
+          <t>Offline / Static mode</t>
         </is>
       </c>
       <c r="G25" s="19" t="inlineStr">
@@ -18644,7 +18641,7 @@
       </c>
       <c r="F26" s="21" t="inlineStr">
         <is>
-          <t>All assertions met</t>
+          <t>Offline / Static mode</t>
         </is>
       </c>
       <c r="G26" s="21" t="inlineStr">
@@ -18681,7 +18678,7 @@
       </c>
       <c r="F27" s="19" t="inlineStr">
         <is>
-          <t>All assertions met</t>
+          <t>Offline / Static mode</t>
         </is>
       </c>
       <c r="G27" s="19" t="inlineStr">
@@ -18718,7 +18715,7 @@
       </c>
       <c r="F28" s="21" t="inlineStr">
         <is>
-          <t>All assertions met</t>
+          <t>Offline / Static mode</t>
         </is>
       </c>
       <c r="G28" s="21" t="inlineStr">
@@ -18755,7 +18752,7 @@
       </c>
       <c r="F29" s="19" t="inlineStr">
         <is>
-          <t>All assertions met</t>
+          <t>Offline / Static mode</t>
         </is>
       </c>
       <c r="G29" s="19" t="inlineStr">
@@ -18792,7 +18789,7 @@
       </c>
       <c r="F30" s="21" t="inlineStr">
         <is>
-          <t>All assertions met</t>
+          <t>Offline / Static mode</t>
         </is>
       </c>
       <c r="G30" s="21" t="inlineStr">
@@ -18829,7 +18826,7 @@
       </c>
       <c r="F31" s="19" t="inlineStr">
         <is>
-          <t>All assertions met</t>
+          <t>Offline / Static mode</t>
         </is>
       </c>
       <c r="G31" s="19" t="inlineStr">
@@ -18866,7 +18863,7 @@
       </c>
       <c r="F32" s="21" t="inlineStr">
         <is>
-          <t>All assertions met</t>
+          <t>Offline / Static mode</t>
         </is>
       </c>
       <c r="G32" s="21" t="inlineStr">
@@ -18902,7 +18899,7 @@
   </cols>
   <sheetData>
     <row r="1" ht="28" customHeight="1">
-      <c r="A1" s="23" t="inlineStr">
+      <c r="A1" s="22" t="inlineStr">
         <is>
           <t>🌐  Web Tests — 80 cases | ✅ 80 Pass | ❌ 0 Fail</t>
         </is>
@@ -18973,7 +18970,7 @@
       </c>
       <c r="F3" s="19" t="inlineStr">
         <is>
-          <t>All assertions met</t>
+          <t>Offline / Static mode</t>
         </is>
       </c>
       <c r="G3" s="19" t="inlineStr">
@@ -19010,7 +19007,7 @@
       </c>
       <c r="F4" s="21" t="inlineStr">
         <is>
-          <t>All assertions met</t>
+          <t>Offline / Static mode</t>
         </is>
       </c>
       <c r="G4" s="21" t="inlineStr">
@@ -19047,7 +19044,7 @@
       </c>
       <c r="F5" s="19" t="inlineStr">
         <is>
-          <t>All assertions met</t>
+          <t>Offline / Static mode</t>
         </is>
       </c>
       <c r="G5" s="19" t="inlineStr">
@@ -19084,7 +19081,7 @@
       </c>
       <c r="F6" s="21" t="inlineStr">
         <is>
-          <t>All assertions met</t>
+          <t>Offline / Static mode</t>
         </is>
       </c>
       <c r="G6" s="21" t="inlineStr">
@@ -19121,7 +19118,7 @@
       </c>
       <c r="F7" s="19" t="inlineStr">
         <is>
-          <t>All assertions met</t>
+          <t>Offline / Static mode</t>
         </is>
       </c>
       <c r="G7" s="19" t="inlineStr">
@@ -19158,7 +19155,7 @@
       </c>
       <c r="F8" s="21" t="inlineStr">
         <is>
-          <t>All assertions met</t>
+          <t>Offline / Static mode</t>
         </is>
       </c>
       <c r="G8" s="21" t="inlineStr">
@@ -19195,7 +19192,7 @@
       </c>
       <c r="F9" s="19" t="inlineStr">
         <is>
-          <t>All assertions met</t>
+          <t>Offline / Static mode</t>
         </is>
       </c>
       <c r="G9" s="19" t="inlineStr">
@@ -19232,7 +19229,7 @@
       </c>
       <c r="F10" s="21" t="inlineStr">
         <is>
-          <t>All assertions met</t>
+          <t>Offline / Static mode</t>
         </is>
       </c>
       <c r="G10" s="21" t="inlineStr">
@@ -19269,7 +19266,7 @@
       </c>
       <c r="F11" s="19" t="inlineStr">
         <is>
-          <t>All assertions met</t>
+          <t>Offline / Static mode</t>
         </is>
       </c>
       <c r="G11" s="19" t="inlineStr">
@@ -19306,7 +19303,7 @@
       </c>
       <c r="F12" s="21" t="inlineStr">
         <is>
-          <t>All assertions met</t>
+          <t>Offline / Static mode</t>
         </is>
       </c>
       <c r="G12" s="21" t="inlineStr">
@@ -19343,7 +19340,7 @@
       </c>
       <c r="F13" s="19" t="inlineStr">
         <is>
-          <t>All assertions met</t>
+          <t>Offline / Static mode</t>
         </is>
       </c>
       <c r="G13" s="19" t="inlineStr">
@@ -19380,7 +19377,7 @@
       </c>
       <c r="F14" s="21" t="inlineStr">
         <is>
-          <t>All assertions met</t>
+          <t>Offline / Static mode</t>
         </is>
       </c>
       <c r="G14" s="21" t="inlineStr">
@@ -19417,7 +19414,7 @@
       </c>
       <c r="F15" s="19" t="inlineStr">
         <is>
-          <t>All assertions met</t>
+          <t>Offline / Static mode</t>
         </is>
       </c>
       <c r="G15" s="19" t="inlineStr">
@@ -19454,7 +19451,7 @@
       </c>
       <c r="F16" s="21" t="inlineStr">
         <is>
-          <t>All assertions met</t>
+          <t>Offline / Static mode</t>
         </is>
       </c>
       <c r="G16" s="21" t="inlineStr">
@@ -19491,7 +19488,7 @@
       </c>
       <c r="F17" s="19" t="inlineStr">
         <is>
-          <t>All assertions met</t>
+          <t>Offline / Static mode</t>
         </is>
       </c>
       <c r="G17" s="19" t="inlineStr">
@@ -19528,7 +19525,7 @@
       </c>
       <c r="F18" s="21" t="inlineStr">
         <is>
-          <t>All assertions met</t>
+          <t>Offline / Static mode</t>
         </is>
       </c>
       <c r="G18" s="21" t="inlineStr">
@@ -19565,7 +19562,7 @@
       </c>
       <c r="F19" s="19" t="inlineStr">
         <is>
-          <t>All assertions met</t>
+          <t>Offline / Static mode</t>
         </is>
       </c>
       <c r="G19" s="19" t="inlineStr">
@@ -19602,7 +19599,7 @@
       </c>
       <c r="F20" s="21" t="inlineStr">
         <is>
-          <t>All assertions met</t>
+          <t>Offline / Static mode</t>
         </is>
       </c>
       <c r="G20" s="21" t="inlineStr">
@@ -19639,7 +19636,7 @@
       </c>
       <c r="F21" s="19" t="inlineStr">
         <is>
-          <t>All assertions met</t>
+          <t>Offline / Static mode</t>
         </is>
       </c>
       <c r="G21" s="19" t="inlineStr">
@@ -19676,7 +19673,7 @@
       </c>
       <c r="F22" s="21" t="inlineStr">
         <is>
-          <t>All assertions met</t>
+          <t>Offline / Static mode</t>
         </is>
       </c>
       <c r="G22" s="21" t="inlineStr">
@@ -19713,7 +19710,7 @@
       </c>
       <c r="F23" s="19" t="inlineStr">
         <is>
-          <t>All assertions met</t>
+          <t>Offline / Static mode</t>
         </is>
       </c>
       <c r="G23" s="19" t="inlineStr">
@@ -19750,7 +19747,7 @@
       </c>
       <c r="F24" s="21" t="inlineStr">
         <is>
-          <t>All assertions met</t>
+          <t>Offline / Static mode</t>
         </is>
       </c>
       <c r="G24" s="21" t="inlineStr">
@@ -19787,7 +19784,7 @@
       </c>
       <c r="F25" s="19" t="inlineStr">
         <is>
-          <t>All assertions met</t>
+          <t>Offline / Static mode</t>
         </is>
       </c>
       <c r="G25" s="19" t="inlineStr">
@@ -19824,7 +19821,7 @@
       </c>
       <c r="F26" s="21" t="inlineStr">
         <is>
-          <t>All assertions met</t>
+          <t>Offline / Static mode</t>
         </is>
       </c>
       <c r="G26" s="21" t="inlineStr">
@@ -19861,7 +19858,7 @@
       </c>
       <c r="F27" s="19" t="inlineStr">
         <is>
-          <t>All assertions met</t>
+          <t>Offline / Static mode</t>
         </is>
       </c>
       <c r="G27" s="19" t="inlineStr">
@@ -19898,7 +19895,7 @@
       </c>
       <c r="F28" s="21" t="inlineStr">
         <is>
-          <t>All assertions met</t>
+          <t>Offline / Static mode</t>
         </is>
       </c>
       <c r="G28" s="21" t="inlineStr">
@@ -19935,7 +19932,7 @@
       </c>
       <c r="F29" s="19" t="inlineStr">
         <is>
-          <t>All assertions met</t>
+          <t>Offline / Static mode</t>
         </is>
       </c>
       <c r="G29" s="19" t="inlineStr">
@@ -19972,7 +19969,7 @@
       </c>
       <c r="F30" s="21" t="inlineStr">
         <is>
-          <t>All assertions met</t>
+          <t>Offline / Static mode</t>
         </is>
       </c>
       <c r="G30" s="21" t="inlineStr">
@@ -20009,7 +20006,7 @@
       </c>
       <c r="F31" s="19" t="inlineStr">
         <is>
-          <t>All assertions met</t>
+          <t>Offline / Static mode</t>
         </is>
       </c>
       <c r="G31" s="19" t="inlineStr">
@@ -20046,7 +20043,7 @@
       </c>
       <c r="F32" s="21" t="inlineStr">
         <is>
-          <t>All assertions met</t>
+          <t>Offline / Static mode</t>
         </is>
       </c>
       <c r="G32" s="21" t="inlineStr">
@@ -20083,7 +20080,7 @@
       </c>
       <c r="F33" s="19" t="inlineStr">
         <is>
-          <t>All assertions met</t>
+          <t>Offline / Static mode</t>
         </is>
       </c>
       <c r="G33" s="19" t="inlineStr">
@@ -20120,7 +20117,7 @@
       </c>
       <c r="F34" s="21" t="inlineStr">
         <is>
-          <t>All assertions met</t>
+          <t>Offline / Static mode</t>
         </is>
       </c>
       <c r="G34" s="21" t="inlineStr">
@@ -20157,7 +20154,7 @@
       </c>
       <c r="F35" s="19" t="inlineStr">
         <is>
-          <t>All assertions met</t>
+          <t>Offline / Static mode</t>
         </is>
       </c>
       <c r="G35" s="19" t="inlineStr">
@@ -20194,7 +20191,7 @@
       </c>
       <c r="F36" s="21" t="inlineStr">
         <is>
-          <t>All assertions met</t>
+          <t>Offline / Static mode</t>
         </is>
       </c>
       <c r="G36" s="21" t="inlineStr">
@@ -20231,7 +20228,7 @@
       </c>
       <c r="F37" s="19" t="inlineStr">
         <is>
-          <t>All assertions met</t>
+          <t>Offline / Static mode</t>
         </is>
       </c>
       <c r="G37" s="19" t="inlineStr">
@@ -20268,7 +20265,7 @@
       </c>
       <c r="F38" s="21" t="inlineStr">
         <is>
-          <t>All assertions met</t>
+          <t>Offline / Static mode</t>
         </is>
       </c>
       <c r="G38" s="21" t="inlineStr">
@@ -20305,7 +20302,7 @@
       </c>
       <c r="F39" s="19" t="inlineStr">
         <is>
-          <t>All assertions met</t>
+          <t>Offline / Static mode</t>
         </is>
       </c>
       <c r="G39" s="19" t="inlineStr">
@@ -20342,7 +20339,7 @@
       </c>
       <c r="F40" s="21" t="inlineStr">
         <is>
-          <t>All assertions met</t>
+          <t>Offline / Static mode</t>
         </is>
       </c>
       <c r="G40" s="21" t="inlineStr">
@@ -20379,7 +20376,7 @@
       </c>
       <c r="F41" s="19" t="inlineStr">
         <is>
-          <t>All assertions met</t>
+          <t>Offline / Static mode</t>
         </is>
       </c>
       <c r="G41" s="19" t="inlineStr">
@@ -20416,7 +20413,7 @@
       </c>
       <c r="F42" s="21" t="inlineStr">
         <is>
-          <t>All assertions met</t>
+          <t>Offline / Static mode</t>
         </is>
       </c>
       <c r="G42" s="21" t="inlineStr">
@@ -20453,7 +20450,7 @@
       </c>
       <c r="F43" s="19" t="inlineStr">
         <is>
-          <t>All assertions met</t>
+          <t>Offline / Static mode</t>
         </is>
       </c>
       <c r="G43" s="19" t="inlineStr">
@@ -20490,7 +20487,7 @@
       </c>
       <c r="F44" s="21" t="inlineStr">
         <is>
-          <t>All assertions met</t>
+          <t>Offline / Static mode</t>
         </is>
       </c>
       <c r="G44" s="21" t="inlineStr">
@@ -20527,7 +20524,7 @@
       </c>
       <c r="F45" s="19" t="inlineStr">
         <is>
-          <t>All assertions met</t>
+          <t>Offline / Static mode</t>
         </is>
       </c>
       <c r="G45" s="19" t="inlineStr">
@@ -20564,7 +20561,7 @@
       </c>
       <c r="F46" s="21" t="inlineStr">
         <is>
-          <t>All assertions met</t>
+          <t>Offline / Static mode</t>
         </is>
       </c>
       <c r="G46" s="21" t="inlineStr">
@@ -20601,7 +20598,7 @@
       </c>
       <c r="F47" s="19" t="inlineStr">
         <is>
-          <t>All assertions met</t>
+          <t>Offline / Static mode</t>
         </is>
       </c>
       <c r="G47" s="19" t="inlineStr">
@@ -20638,7 +20635,7 @@
       </c>
       <c r="F48" s="21" t="inlineStr">
         <is>
-          <t>All assertions met</t>
+          <t>Offline / Static mode</t>
         </is>
       </c>
       <c r="G48" s="21" t="inlineStr">
@@ -20675,7 +20672,7 @@
       </c>
       <c r="F49" s="19" t="inlineStr">
         <is>
-          <t>All assertions met</t>
+          <t>Offline / Static mode</t>
         </is>
       </c>
       <c r="G49" s="19" t="inlineStr">
@@ -20712,7 +20709,7 @@
       </c>
       <c r="F50" s="21" t="inlineStr">
         <is>
-          <t>All assertions met</t>
+          <t>Offline / Static mode</t>
         </is>
       </c>
       <c r="G50" s="21" t="inlineStr">
@@ -20749,7 +20746,7 @@
       </c>
       <c r="F51" s="19" t="inlineStr">
         <is>
-          <t>All assertions met</t>
+          <t>Offline / Static mode</t>
         </is>
       </c>
       <c r="G51" s="19" t="inlineStr">
@@ -20786,7 +20783,7 @@
       </c>
       <c r="F52" s="21" t="inlineStr">
         <is>
-          <t>All assertions met</t>
+          <t>Offline / Static mode</t>
         </is>
       </c>
       <c r="G52" s="21" t="inlineStr">
@@ -20823,7 +20820,7 @@
       </c>
       <c r="F53" s="19" t="inlineStr">
         <is>
-          <t>All assertions met</t>
+          <t>Offline / Static mode</t>
         </is>
       </c>
       <c r="G53" s="19" t="inlineStr">
@@ -20860,7 +20857,7 @@
       </c>
       <c r="F54" s="21" t="inlineStr">
         <is>
-          <t>All assertions met</t>
+          <t>Offline / Static mode</t>
         </is>
       </c>
       <c r="G54" s="21" t="inlineStr">
@@ -20897,7 +20894,7 @@
       </c>
       <c r="F55" s="19" t="inlineStr">
         <is>
-          <t>All assertions met</t>
+          <t>Offline / Static mode</t>
         </is>
       </c>
       <c r="G55" s="19" t="inlineStr">
@@ -20934,7 +20931,7 @@
       </c>
       <c r="F56" s="21" t="inlineStr">
         <is>
-          <t>All assertions met</t>
+          <t>Offline / Static mode</t>
         </is>
       </c>
       <c r="G56" s="21" t="inlineStr">
@@ -20971,7 +20968,7 @@
       </c>
       <c r="F57" s="19" t="inlineStr">
         <is>
-          <t>All assertions met</t>
+          <t>Offline / Static mode</t>
         </is>
       </c>
       <c r="G57" s="19" t="inlineStr">
@@ -21008,7 +21005,7 @@
       </c>
       <c r="F58" s="21" t="inlineStr">
         <is>
-          <t>All assertions met</t>
+          <t>Offline / Static mode</t>
         </is>
       </c>
       <c r="G58" s="21" t="inlineStr">
@@ -21045,7 +21042,7 @@
       </c>
       <c r="F59" s="19" t="inlineStr">
         <is>
-          <t>All assertions met</t>
+          <t>Offline / Static mode</t>
         </is>
       </c>
       <c r="G59" s="19" t="inlineStr">
@@ -21082,7 +21079,7 @@
       </c>
       <c r="F60" s="21" t="inlineStr">
         <is>
-          <t>All assertions met</t>
+          <t>Offline / Static mode</t>
         </is>
       </c>
       <c r="G60" s="21" t="inlineStr">
@@ -21119,7 +21116,7 @@
       </c>
       <c r="F61" s="19" t="inlineStr">
         <is>
-          <t>All assertions met</t>
+          <t>Offline / Static mode</t>
         </is>
       </c>
       <c r="G61" s="19" t="inlineStr">
@@ -21156,7 +21153,7 @@
       </c>
       <c r="F62" s="21" t="inlineStr">
         <is>
-          <t>All assertions met</t>
+          <t>Offline / Static mode</t>
         </is>
       </c>
       <c r="G62" s="21" t="inlineStr">
@@ -21193,7 +21190,7 @@
       </c>
       <c r="F63" s="19" t="inlineStr">
         <is>
-          <t>All assertions met</t>
+          <t>Offline / Static mode</t>
         </is>
       </c>
       <c r="G63" s="19" t="inlineStr">
@@ -21230,7 +21227,7 @@
       </c>
       <c r="F64" s="21" t="inlineStr">
         <is>
-          <t>All assertions met</t>
+          <t>Offline / Static mode</t>
         </is>
       </c>
       <c r="G64" s="21" t="inlineStr">
@@ -21267,7 +21264,7 @@
       </c>
       <c r="F65" s="19" t="inlineStr">
         <is>
-          <t>All assertions met</t>
+          <t>Offline / Static mode</t>
         </is>
       </c>
       <c r="G65" s="19" t="inlineStr">
@@ -21304,7 +21301,7 @@
       </c>
       <c r="F66" s="21" t="inlineStr">
         <is>
-          <t>All assertions met</t>
+          <t>Offline / Static mode</t>
         </is>
       </c>
       <c r="G66" s="21" t="inlineStr">
@@ -21341,7 +21338,7 @@
       </c>
       <c r="F67" s="19" t="inlineStr">
         <is>
-          <t>All assertions met</t>
+          <t>Offline / Static mode</t>
         </is>
       </c>
       <c r="G67" s="19" t="inlineStr">
@@ -21378,7 +21375,7 @@
       </c>
       <c r="F68" s="21" t="inlineStr">
         <is>
-          <t>All assertions met</t>
+          <t>Offline / Static mode</t>
         </is>
       </c>
       <c r="G68" s="21" t="inlineStr">
@@ -21415,7 +21412,7 @@
       </c>
       <c r="F69" s="19" t="inlineStr">
         <is>
-          <t>All assertions met</t>
+          <t>Offline / Static mode</t>
         </is>
       </c>
       <c r="G69" s="19" t="inlineStr">
@@ -21452,7 +21449,7 @@
       </c>
       <c r="F70" s="21" t="inlineStr">
         <is>
-          <t>All assertions met</t>
+          <t>Offline / Static mode</t>
         </is>
       </c>
       <c r="G70" s="21" t="inlineStr">
@@ -21489,7 +21486,7 @@
       </c>
       <c r="F71" s="19" t="inlineStr">
         <is>
-          <t>All assertions met</t>
+          <t>Offline / Static mode</t>
         </is>
       </c>
       <c r="G71" s="19" t="inlineStr">
@@ -21526,7 +21523,7 @@
       </c>
       <c r="F72" s="21" t="inlineStr">
         <is>
-          <t>All assertions met</t>
+          <t>Offline / Static mode</t>
         </is>
       </c>
       <c r="G72" s="21" t="inlineStr">
@@ -21563,7 +21560,7 @@
       </c>
       <c r="F73" s="19" t="inlineStr">
         <is>
-          <t>All assertions met</t>
+          <t>Offline / Static mode</t>
         </is>
       </c>
       <c r="G73" s="19" t="inlineStr">
@@ -21600,7 +21597,7 @@
       </c>
       <c r="F74" s="21" t="inlineStr">
         <is>
-          <t>All assertions met</t>
+          <t>Offline / Static mode</t>
         </is>
       </c>
       <c r="G74" s="21" t="inlineStr">
@@ -21637,7 +21634,7 @@
       </c>
       <c r="F75" s="19" t="inlineStr">
         <is>
-          <t>All assertions met</t>
+          <t>Offline / Static mode</t>
         </is>
       </c>
       <c r="G75" s="19" t="inlineStr">
@@ -21674,7 +21671,7 @@
       </c>
       <c r="F76" s="21" t="inlineStr">
         <is>
-          <t>All assertions met</t>
+          <t>Offline / Static mode</t>
         </is>
       </c>
       <c r="G76" s="21" t="inlineStr">
@@ -21711,7 +21708,7 @@
       </c>
       <c r="F77" s="19" t="inlineStr">
         <is>
-          <t>All assertions met</t>
+          <t>Offline / Static mode</t>
         </is>
       </c>
       <c r="G77" s="19" t="inlineStr">
@@ -21748,7 +21745,7 @@
       </c>
       <c r="F78" s="21" t="inlineStr">
         <is>
-          <t>All assertions met</t>
+          <t>Offline / Static mode</t>
         </is>
       </c>
       <c r="G78" s="21" t="inlineStr">
@@ -21785,7 +21782,7 @@
       </c>
       <c r="F79" s="19" t="inlineStr">
         <is>
-          <t>All assertions met</t>
+          <t>Offline / Static mode</t>
         </is>
       </c>
       <c r="G79" s="19" t="inlineStr">
@@ -21822,7 +21819,7 @@
       </c>
       <c r="F80" s="21" t="inlineStr">
         <is>
-          <t>All assertions met</t>
+          <t>Offline / Static mode</t>
         </is>
       </c>
       <c r="G80" s="21" t="inlineStr">
@@ -21859,7 +21856,7 @@
       </c>
       <c r="F81" s="19" t="inlineStr">
         <is>
-          <t>All assertions met</t>
+          <t>Offline / Static mode</t>
         </is>
       </c>
       <c r="G81" s="19" t="inlineStr">
@@ -21896,7 +21893,7 @@
       </c>
       <c r="F82" s="21" t="inlineStr">
         <is>
-          <t>All assertions met</t>
+          <t>Offline / Static mode</t>
         </is>
       </c>
       <c r="G82" s="21" t="inlineStr">
@@ -21934,234 +21931,234 @@
       </c>
     </row>
     <row r="3" ht="22" customHeight="1">
-      <c r="A3" s="24" t="inlineStr">
+      <c r="A3" s="23" t="inlineStr">
         <is>
           <t>1️⃣  SETUP</t>
         </is>
       </c>
     </row>
     <row r="4" ht="22" customHeight="1">
-      <c r="A4" s="25" t="inlineStr">
+      <c r="A4" s="24" t="inlineStr">
         <is>
           <t>Install dependencies</t>
         </is>
       </c>
-      <c r="B4" s="26" t="inlineStr">
+      <c r="B4" s="25" t="inlineStr">
         <is>
           <t>pip install -r testing/requirements_test.txt</t>
         </is>
       </c>
     </row>
     <row r="5" ht="22" customHeight="1">
-      <c r="A5" s="24" t="inlineStr">
+      <c r="A5" s="23" t="inlineStr">
         <is>
           <t>2️⃣  RUN ALL TESTS (Full Suite)</t>
         </is>
       </c>
     </row>
     <row r="6" ht="22" customHeight="1">
-      <c r="A6" s="25" t="inlineStr">
+      <c r="A6" s="24" t="inlineStr">
         <is>
           <t>All tests</t>
         </is>
       </c>
-      <c r="B6" s="26" t="inlineStr">
+      <c r="B6" s="25" t="inlineStr">
         <is>
           <t>cd testing &amp;&amp; pytest api/ unit/ selenium_web/ functional/ --tb=short -v --junitxml=reports/master_junit.xml</t>
         </is>
       </c>
     </row>
     <row r="7" ht="22" customHeight="1">
-      <c r="A7" s="24" t="inlineStr">
+      <c r="A7" s="23" t="inlineStr">
         <is>
           <t>3️⃣  RUN BY SUITE</t>
         </is>
       </c>
     </row>
     <row r="8" ht="22" customHeight="1">
-      <c r="A8" s="25" t="inlineStr">
+      <c r="A8" s="24" t="inlineStr">
         <is>
           <t>API functional tests</t>
         </is>
       </c>
-      <c r="B8" s="26" t="inlineStr">
+      <c r="B8" s="25" t="inlineStr">
         <is>
           <t>pytest testing/api/test_api_functional.py -v --junitxml=testing/reports/api_junit.xml</t>
         </is>
       </c>
     </row>
     <row r="9" ht="22" customHeight="1">
-      <c r="A9" s="25" t="inlineStr">
+      <c r="A9" s="24" t="inlineStr">
         <is>
           <t>UI/UX validation tests</t>
         </is>
       </c>
-      <c r="B9" s="26" t="inlineStr">
+      <c r="B9" s="25" t="inlineStr">
         <is>
           <t>pytest testing/api/test_uiux_validation.py -v --junitxml=testing/reports/uiux_junit.xml</t>
         </is>
       </c>
     </row>
     <row r="10" ht="22" customHeight="1">
-      <c r="A10" s="25" t="inlineStr">
+      <c r="A10" s="24" t="inlineStr">
         <is>
           <t>Unit tests only</t>
         </is>
       </c>
-      <c r="B10" s="26" t="inlineStr">
+      <c r="B10" s="25" t="inlineStr">
         <is>
           <t>pytest testing/unit/test_unit.py -v --junitxml=testing/reports/unit_junit.xml</t>
         </is>
       </c>
     </row>
     <row r="11" ht="22" customHeight="1">
-      <c r="A11" s="25" t="inlineStr">
+      <c r="A11" s="24" t="inlineStr">
         <is>
           <t>Selenium web tests</t>
         </is>
       </c>
-      <c r="B11" s="26" t="inlineStr">
+      <c r="B11" s="25" t="inlineStr">
         <is>
           <t>pytest testing/selenium_web/test_selenium_web.py -v --junitxml=testing/reports/selenium_junit.xml</t>
         </is>
       </c>
     </row>
     <row r="12" ht="22" customHeight="1">
-      <c r="A12" s="25" t="inlineStr">
+      <c r="A12" s="24" t="inlineStr">
         <is>
           <t>Functional E2E tests</t>
         </is>
       </c>
-      <c r="B12" s="26" t="inlineStr">
+      <c r="B12" s="25" t="inlineStr">
         <is>
           <t>pytest testing/functional/test_functionality.py -v --junitxml=testing/reports/functional_junit.xml</t>
         </is>
       </c>
     </row>
     <row r="13" ht="22" customHeight="1">
-      <c r="A13" s="25" t="inlineStr">
+      <c r="A13" s="24" t="inlineStr">
         <is>
           <t>Appium mobile tests (Node)</t>
         </is>
       </c>
-      <c r="B13" s="26" t="inlineStr">
+      <c r="B13" s="25" t="inlineStr">
         <is>
           <t>cd appium_node &amp;&amp; npm install &amp;&amp; npm test</t>
         </is>
       </c>
     </row>
     <row r="14" ht="22" customHeight="1">
-      <c r="A14" s="24" t="inlineStr">
+      <c r="A14" s="23" t="inlineStr">
         <is>
           <t>4️⃣  GENERATE REPORTS</t>
         </is>
       </c>
     </row>
     <row r="15" ht="22" customHeight="1">
-      <c r="A15" s="25" t="inlineStr">
+      <c r="A15" s="24" t="inlineStr">
         <is>
           <t>Full XLSX report</t>
         </is>
       </c>
-      <c r="B15" s="26" t="inlineStr">
+      <c r="B15" s="25" t="inlineStr">
         <is>
           <t>cd testing &amp;&amp; python generate_test_report.py</t>
         </is>
       </c>
     </row>
     <row r="16" ht="22" customHeight="1">
-      <c r="A16" s="25" t="inlineStr">
+      <c r="A16" s="24" t="inlineStr">
         <is>
           <t>Issues report only</t>
         </is>
       </c>
-      <c r="B16" s="26" t="inlineStr">
+      <c r="B16" s="25" t="inlineStr">
         <is>
           <t>cd testing &amp;&amp; python generate_issues_report.py</t>
         </is>
       </c>
     </row>
     <row r="17" ht="22" customHeight="1">
-      <c r="A17" s="25" t="inlineStr">
+      <c r="A17" s="24" t="inlineStr">
         <is>
           <t>Security XLSX report</t>
         </is>
       </c>
-      <c r="B17" s="26" t="inlineStr">
+      <c r="B17" s="25" t="inlineStr">
         <is>
           <t>python scripts/generate_security_xlsx.py</t>
         </is>
       </c>
     </row>
     <row r="18" ht="22" customHeight="1">
-      <c r="A18" s="24" t="inlineStr">
+      <c r="A18" s="23" t="inlineStr">
         <is>
           <t>5️⃣  ENVIRONMENT VARIABLES</t>
         </is>
       </c>
     </row>
     <row r="19" ht="22" customHeight="1">
-      <c r="A19" s="25" t="inlineStr">
+      <c r="A19" s="24" t="inlineStr">
         <is>
           <t>Set API base URL</t>
         </is>
       </c>
-      <c r="B19" s="26" t="inlineStr">
+      <c r="B19" s="25" t="inlineStr">
         <is>
           <t>export API_BASE_URL=http://10.135.142.53:8000</t>
         </is>
       </c>
     </row>
     <row r="20" ht="22" customHeight="1">
-      <c r="A20" s="25" t="inlineStr">
+      <c r="A20" s="24" t="inlineStr">
         <is>
           <t>Set Selenium URL</t>
         </is>
       </c>
-      <c r="B20" s="26" t="inlineStr">
+      <c r="B20" s="25" t="inlineStr">
         <is>
           <t>export SELENIUM_BASE_URL=https://tilaksai99.github.io/pddtesting</t>
         </is>
       </c>
     </row>
     <row r="21" ht="22" customHeight="1">
-      <c r="A21" s="25" t="inlineStr">
+      <c r="A21" s="24" t="inlineStr">
         <is>
           <t>Set Appium host/port</t>
         </is>
       </c>
-      <c r="B21" s="26" t="inlineStr">
+      <c r="B21" s="25" t="inlineStr">
         <is>
           <t>export APPIUM_HOST=127.0.0.1 &amp;&amp; export APPIUM_PORT=4723</t>
         </is>
       </c>
     </row>
     <row r="22" ht="22" customHeight="1">
-      <c r="A22" s="24" t="inlineStr">
+      <c r="A22" s="23" t="inlineStr">
         <is>
           <t>6️⃣  GITHUB ACTIONS</t>
         </is>
       </c>
     </row>
     <row r="23" ht="22" customHeight="1">
-      <c r="A23" s="25" t="inlineStr">
+      <c r="A23" s="24" t="inlineStr">
         <is>
           <t>Trigger pipeline</t>
         </is>
       </c>
-      <c r="B23" s="26" t="inlineStr">
+      <c r="B23" s="25" t="inlineStr">
         <is>
           <t>git push → master-test-pipeline.yml runs automatically</t>
         </is>
       </c>
     </row>
     <row r="24" ht="22" customHeight="1">
-      <c r="A24" s="25" t="inlineStr">
+      <c r="A24" s="24" t="inlineStr">
         <is>
           <t>Download reports</t>
         </is>
       </c>
-      <c r="B24" s="26" t="inlineStr">
+      <c r="B24" s="25" t="inlineStr">
         <is>
           <t>GitHub → Actions → Run → Artifacts → master-test-report.xlsx</t>
         </is>
